--- a/data/k-props/2026-08-15.xlsx
+++ b/data/k-props/2026-08-15.xlsx
@@ -130,84 +130,87 @@
     <t>projection</t>
   </si>
   <si>
-    <t>2026-08-15</t>
+    <t>08/15/2026</t>
+  </si>
+  <si>
+    <t>Anthony Kay</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
   </si>
   <si>
     <t>Troy Melton</t>
   </si>
   <si>
-    <t>Chicago White Sox @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Anthony Kay</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Chicago Cubs</t>
   </si>
   <si>
     <t>Matthew Boyd</t>
   </si>
   <si>
-    <t>St. Louis Cardinals @ Chicago Cubs</t>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Braydon Fisher</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Michael Lorenzen</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
   </si>
   <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
     <t>Logan Webb</t>
   </si>
   <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Michael Lorenzen</t>
-  </si>
-  <si>
     <t>Brad Lord</t>
   </si>
   <si>
     <t>Washington Nationals @ New York Mets</t>
   </si>
   <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
     <t>Sean Manaea</t>
   </si>
   <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
     <t>Ian Seymour</t>
   </si>
   <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
     <t>Ryan Gusto</t>
   </si>
   <si>
@@ -235,67 +238,64 @@
     <t>Hayden Wesneski</t>
   </si>
   <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Justin Wrobleski</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
     <t>Jesus Luzardo</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Justin Wrobleski</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
-  </si>
-  <si>
     <t>JT Ginn</t>
-  </si>
-  <si>
-    <t>Braydon Fisher</t>
-  </si>
-  <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
   </si>
 </sst>
 </file>
@@ -809,13 +809,13 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
         <v>115</v>
       </c>
       <c r="E2">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -827,7 +827,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -839,43 +839,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2248</v>
+        <v>0.1811</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P2">
-        <v>3.84</v>
+        <v>4.47</v>
       </c>
       <c r="Q2">
-        <v>0.2373</v>
+        <v>0.1983</v>
       </c>
       <c r="R2">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2392</v>
+        <v>0.1831</v>
       </c>
       <c r="U2">
-        <v>0.2457</v>
+        <v>0.2045</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2369</v>
+        <v>0.2277</v>
       </c>
       <c r="X2">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y2">
-        <v>1.0768</v>
+        <v>0.9736</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -884,22 +884,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.35</v>
+        <v>3.32</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2294</v>
+        <v>0.1874</v>
       </c>
       <c r="AG2">
-        <v>1.0886</v>
+        <v>0.822</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.35</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -910,13 +910,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
         <v>115</v>
       </c>
       <c r="E3">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -928,7 +928,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -940,43 +940,43 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1811</v>
+        <v>0.2248</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P3">
-        <v>4.47</v>
+        <v>3.84</v>
       </c>
       <c r="Q3">
-        <v>0.1983</v>
+        <v>0.2373</v>
       </c>
       <c r="R3">
-        <v>0.367</v>
+        <v>0.371</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.1831</v>
+        <v>0.2392</v>
       </c>
       <c r="U3">
-        <v>0.2045</v>
+        <v>0.2457</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2277</v>
+        <v>0.2369</v>
       </c>
       <c r="X3">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y3">
-        <v>0.9736</v>
+        <v>1.0768</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -985,22 +985,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.37</v>
+        <v>6.26</v>
       </c>
       <c r="AE3" t="s">
         <v>47</v>
       </c>
       <c r="AF3">
-        <v>0.1874</v>
+        <v>0.2294</v>
       </c>
       <c r="AG3">
-        <v>0.8333</v>
+        <v>1.0738</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.37</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1011,13 +1011,13 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-106</v>
+        <v>114</v>
       </c>
       <c r="E4">
-        <v>-106</v>
+        <v>-125</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
@@ -1029,7 +1029,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1041,43 +1041,43 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2006</v>
+        <v>0.1657</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="P4">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="Q4">
-        <v>0.1429</v>
+        <v>0.1696</v>
       </c>
       <c r="R4">
-        <v>0.399</v>
+        <v>0.359</v>
       </c>
       <c r="S4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2068</v>
+        <v>0.2474</v>
       </c>
       <c r="U4">
-        <v>0.1928</v>
+        <v>0.2364</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.1835</v>
+        <v>0.2174</v>
       </c>
       <c r="X4">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y4">
-        <v>0.9586</v>
+        <v>0.9668</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1086,22 +1086,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1775</v>
+        <v>0.1671</v>
       </c>
       <c r="AG4">
-        <v>0.941</v>
+        <v>1.1106</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.76</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1109,16 +1109,16 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>114</v>
+        <v>-106</v>
       </c>
       <c r="E5">
-        <v>-125</v>
+        <v>-106</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1142,43 +1142,43 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.1657</v>
+        <v>0.2006</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="P5">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="Q5">
-        <v>0.1696</v>
+        <v>0.1429</v>
       </c>
       <c r="R5">
-        <v>0.359</v>
+        <v>0.399</v>
       </c>
       <c r="S5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2303</v>
+        <v>0.2533</v>
       </c>
       <c r="U5">
-        <v>0.228</v>
+        <v>0.2142</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>0.2174</v>
+        <v>0.1835</v>
       </c>
       <c r="X5">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y5">
-        <v>0.99</v>
+        <v>0.9265</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1187,22 +1187,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.87</v>
+        <v>4.4</v>
       </c>
       <c r="AE5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1671</v>
+        <v>0.1775</v>
       </c>
       <c r="AG5">
-        <v>1.0478</v>
+        <v>1.137</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.87</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1210,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>6.5</v>
@@ -1222,7 +1222,7 @@
         <v>-138</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>822775</v>
@@ -1261,13 +1261,13 @@
         <v>0.355</v>
       </c>
       <c r="S6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.1977</v>
+        <v>0.243</v>
       </c>
       <c r="U6">
-        <v>0.1824</v>
+        <v>0.2233</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1276,10 +1276,10 @@
         <v>0.1893</v>
       </c>
       <c r="X6">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y6">
-        <v>0.985</v>
+        <v>1.0898</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1288,22 +1288,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>7.14</v>
+        <v>9.58</v>
       </c>
       <c r="AE6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF6">
         <v>0.348</v>
       </c>
       <c r="AG6">
-        <v>0.8997</v>
+        <v>1.0905</v>
       </c>
       <c r="AH6">
-        <v>-0.8</v>
+        <v>-0.77</v>
       </c>
       <c r="AM6">
-        <v>6.34</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,76 +1311,67 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7">
+        <v>822775</v>
+      </c>
+      <c r="H7" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>-115</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>823184</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
       <c r="I7">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.1914</v>
+        <v>0.2298</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="P7">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="Q7">
-        <v>0.1825</v>
+        <v>0.2083</v>
       </c>
       <c r="R7">
-        <v>0.387</v>
+        <v>0.107</v>
       </c>
       <c r="S7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.228</v>
+        <v>0.2544</v>
       </c>
       <c r="U7">
-        <v>0.2254</v>
+        <v>0.2579</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2164</v>
+        <v>0.2434</v>
       </c>
       <c r="X7">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y7">
-        <v>1.0137</v>
+        <v>1.0475</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1389,22 +1380,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>5.06</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.188</v>
+        <v>0.2275</v>
       </c>
       <c r="AG7">
-        <v>1.0373</v>
+        <v>1.1419</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>5.06</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1412,7 +1403,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1424,7 +1415,7 @@
         <v>-140</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>823184</v>
@@ -1463,7 +1454,7 @@
         <v>0.338</v>
       </c>
       <c r="S8" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T8">
         <v>0.2156</v>
@@ -1478,7 +1469,7 @@
         <v>0.2021</v>
       </c>
       <c r="X8">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y8">
         <v>0.9683</v>
@@ -1490,22 +1481,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF8">
         <v>0.1286</v>
       </c>
       <c r="AG8">
-        <v>0.9811</v>
+        <v>0.9678</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1513,31 +1504,31 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>-151</v>
+        <v>-115</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>823588</v>
+        <v>823184</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1546,43 +1537,43 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2137</v>
+        <v>0.1914</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="P9">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="Q9">
-        <v>0.2273</v>
+        <v>0.1825</v>
       </c>
       <c r="R9">
-        <v>0.099</v>
+        <v>0.387</v>
       </c>
       <c r="S9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T9">
-        <v>0.2411</v>
+        <v>0.228</v>
       </c>
       <c r="U9">
-        <v>0.2383</v>
+        <v>0.2254</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2248</v>
+        <v>0.2164</v>
       </c>
       <c r="X9">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y9">
-        <v>0.9942</v>
+        <v>1.0137</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1591,22 +1582,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2151</v>
+        <v>0.188</v>
       </c>
       <c r="AG9">
-        <v>1.0972</v>
+        <v>1.0232</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>2.49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1614,31 +1605,31 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>3.5</v>
+      </c>
+      <c r="D10">
+        <v>133</v>
+      </c>
+      <c r="E10">
+        <v>-151</v>
+      </c>
+      <c r="F10" t="s">
         <v>61</v>
-      </c>
-      <c r="C10">
-        <v>5.5</v>
-      </c>
-      <c r="D10">
-        <v>-133</v>
-      </c>
-      <c r="E10">
-        <v>118</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
       </c>
       <c r="G10">
         <v>823588</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1647,43 +1638,43 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2335</v>
+        <v>0.2137</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O10">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="P10">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="Q10">
-        <v>0.256</v>
+        <v>0.2273</v>
       </c>
       <c r="R10">
-        <v>0.385</v>
+        <v>0.099</v>
       </c>
       <c r="S10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T10">
-        <v>0.2088</v>
+        <v>0.2411</v>
       </c>
       <c r="U10">
-        <v>0.2149</v>
+        <v>0.2383</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2345</v>
+        <v>0.2248</v>
       </c>
       <c r="X10">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y10">
-        <v>0.9877</v>
+        <v>0.9942</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1692,22 +1683,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.53</v>
+        <v>2.46</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2421</v>
+        <v>0.2151</v>
       </c>
       <c r="AG10">
-        <v>0.9503</v>
+        <v>1.0823</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>5.53</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1718,25 +1709,25 @@
         <v>62</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>-111</v>
+        <v>-133</v>
       </c>
       <c r="E11">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>822941</v>
+        <v>823588</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1748,43 +1739,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2842</v>
+        <v>0.2335</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="P11">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="Q11">
-        <v>0.3398</v>
+        <v>0.256</v>
       </c>
       <c r="R11">
-        <v>0.34</v>
+        <v>0.385</v>
       </c>
       <c r="S11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T11">
-        <v>0.2888</v>
+        <v>0.2088</v>
       </c>
       <c r="U11">
-        <v>0.2554</v>
+        <v>0.2149</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2573</v>
+        <v>0.2345</v>
       </c>
       <c r="X11">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y11">
-        <v>1.0111</v>
+        <v>0.9877</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1793,22 +1784,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>7.51</v>
+        <v>5.45</v>
       </c>
       <c r="AE11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.3031</v>
+        <v>0.2421</v>
       </c>
       <c r="AG11">
-        <v>1.3142</v>
+        <v>0.9374</v>
       </c>
       <c r="AH11">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>6.71</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1816,7 +1807,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1828,7 +1819,7 @@
         <v>-109</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>822941</v>
@@ -1867,7 +1858,7 @@
         <v>0.346</v>
       </c>
       <c r="S12" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T12">
         <v>0.1806</v>
@@ -1882,7 +1873,7 @@
         <v>0.1896</v>
       </c>
       <c r="X12">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y12">
         <v>0.8948</v>
@@ -1894,22 +1885,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AE12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF12">
         <v>0.2132</v>
       </c>
       <c r="AG12">
-        <v>0.8219</v>
+        <v>0.8107</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1920,25 +1911,25 @@
         <v>65</v>
       </c>
       <c r="C13">
+        <v>6.5</v>
+      </c>
+      <c r="D13">
+        <v>-111</v>
+      </c>
+      <c r="E13">
+        <v>103</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>822941</v>
+      </c>
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13">
         <v>4.5</v>
-      </c>
-      <c r="D13">
-        <v>-103</v>
-      </c>
-      <c r="E13">
-        <v>-104</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>824480</v>
-      </c>
-      <c r="H13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13">
-        <v>4</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1950,43 +1941,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.1991</v>
+        <v>0.2842</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="P13">
-        <v>4.41</v>
+        <v>4.13</v>
       </c>
       <c r="Q13">
-        <v>0.1915</v>
+        <v>0.3398</v>
       </c>
       <c r="R13">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="S13" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T13">
-        <v>0.2482</v>
+        <v>0.2888</v>
       </c>
       <c r="U13">
-        <v>0.2609</v>
+        <v>0.2554</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>0.2532</v>
+        <v>0.2573</v>
       </c>
       <c r="X13">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y13">
-        <v>1.0366</v>
+        <v>1.0111</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1995,22 +1986,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.03</v>
+        <v>7.41</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AF13">
-        <v>0.1966</v>
+        <v>0.3031</v>
       </c>
       <c r="AG13">
-        <v>1.1293</v>
+        <v>1.2964</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM13">
-        <v>4.03</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2018,28 +2009,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>4.5</v>
       </c>
       <c r="D14">
-        <v>-145</v>
+        <v>-103</v>
       </c>
       <c r="E14">
-        <v>125</v>
+        <v>-104</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>824480</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I14">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2051,43 +2042,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1887</v>
+        <v>0.1991</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="P14">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="Q14">
-        <v>0.1875</v>
+        <v>0.1915</v>
       </c>
       <c r="R14">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="S14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T14">
-        <v>0.2453</v>
+        <v>0.2482</v>
       </c>
       <c r="U14">
-        <v>0.2358</v>
+        <v>0.2609</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2115</v>
+        <v>0.2532</v>
       </c>
       <c r="X14">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y14">
-        <v>0.96</v>
+        <v>1.0366</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2096,22 +2087,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.65</v>
+        <v>3.97</v>
       </c>
       <c r="AE14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1882</v>
+        <v>0.1966</v>
       </c>
       <c r="AG14">
-        <v>1.1162</v>
+        <v>1.114</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.65</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2122,25 +2113,25 @@
         <v>69</v>
       </c>
       <c r="C15">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D15">
-        <v>118</v>
+        <v>-145</v>
       </c>
       <c r="E15">
-        <v>-146</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>824400</v>
+        <v>824480</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2149,46 +2140,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2529</v>
+        <v>0.1887</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="P15">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="Q15">
-        <v>0.2935</v>
+        <v>0.1875</v>
       </c>
       <c r="R15">
-        <v>0.315</v>
+        <v>0.39</v>
       </c>
       <c r="S15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T15">
-        <v>0.1514</v>
+        <v>0.2453</v>
       </c>
       <c r="U15">
-        <v>0.1692</v>
+        <v>0.2358</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2154</v>
+        <v>0.2115</v>
       </c>
       <c r="X15">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y15">
-        <v>0.9934</v>
+        <v>0.96</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2197,22 +2188,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.8</v>
+        <v>4.58</v>
       </c>
       <c r="AE15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2657</v>
+        <v>0.1882</v>
       </c>
       <c r="AG15">
-        <v>0.6889</v>
+        <v>1.101</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>3.8</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2220,28 +2211,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16">
+        <v>5.5</v>
+      </c>
+      <c r="D16">
+        <v>118</v>
+      </c>
+      <c r="E16">
+        <v>-146</v>
+      </c>
+      <c r="F16" t="s">
         <v>71</v>
       </c>
-      <c r="C16">
-        <v>4.5</v>
-      </c>
-      <c r="D16">
-        <v>-113</v>
-      </c>
-      <c r="E16">
-        <v>-104</v>
-      </c>
-      <c r="F16" t="s">
-        <v>72</v>
-      </c>
       <c r="G16">
-        <v>824157</v>
+        <v>824400</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2250,46 +2241,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>0.2265</v>
+        <v>0.2529</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="P16">
-        <v>4.05</v>
+        <v>4.36</v>
       </c>
       <c r="Q16">
-        <v>0.1792</v>
+        <v>0.2935</v>
       </c>
       <c r="R16">
-        <v>0.346</v>
+        <v>0.315</v>
       </c>
       <c r="S16" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T16">
-        <v>0.2068</v>
+        <v>0.1514</v>
       </c>
       <c r="U16">
-        <v>0.1978</v>
+        <v>0.1692</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>0.2154</v>
       </c>
       <c r="X16">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y16">
-        <v>0.9979</v>
+        <v>0.9934</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2298,22 +2289,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.39</v>
+        <v>3.74</v>
       </c>
       <c r="AE16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.2102</v>
+        <v>0.2657</v>
       </c>
       <c r="AG16">
-        <v>0.9409</v>
+        <v>0.6795</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.39</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2321,19 +2312,19 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17">
         <v>4.5</v>
       </c>
       <c r="D17">
-        <v>126</v>
+        <v>-113</v>
       </c>
       <c r="E17">
-        <v>-150</v>
+        <v>-104</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>824157</v>
@@ -2342,7 +2333,7 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2354,43 +2345,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.16</v>
+        <v>0.2265</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="P17">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="Q17">
-        <v>0.16</v>
+        <v>0.1792</v>
       </c>
       <c r="R17">
-        <v>0.273</v>
+        <v>0.346</v>
       </c>
       <c r="S17" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T17">
-        <v>0.2013</v>
+        <v>0.2068</v>
       </c>
       <c r="U17">
-        <v>0.1913</v>
+        <v>0.1978</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>0.2251</v>
+        <v>0.2154</v>
       </c>
       <c r="X17">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y17">
-        <v>0.9945</v>
+        <v>0.9979</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2399,22 +2390,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.64</v>
+        <v>4.34</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.16</v>
+        <v>0.2102</v>
       </c>
       <c r="AG17">
-        <v>0.9159</v>
+        <v>0.9281</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>3.64</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2425,31 +2416,73 @@
         <v>74</v>
       </c>
       <c r="C18">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-103</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>-120</v>
+        <v>-150</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s">
-        <v>44</v>
+        <v>73</v>
+      </c>
+      <c r="G18">
+        <v>824157</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I18">
+        <v>6.2</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
+      <c r="M18">
+        <v>0.16</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18">
+        <v>75</v>
+      </c>
+      <c r="P18">
+        <v>4.02</v>
+      </c>
+      <c r="Q18">
+        <v>0.16</v>
+      </c>
+      <c r="R18">
+        <v>0.273</v>
+      </c>
       <c r="S18" t="s">
-        <v>44</v>
-      </c>
-      <c r="V18" t="s">
-        <v>44</v>
+        <v>58</v>
+      </c>
+      <c r="T18">
+        <v>0.2013</v>
+      </c>
+      <c r="U18">
+        <v>0.1913</v>
+      </c>
+      <c r="V18">
+        <v>9</v>
+      </c>
+      <c r="W18">
+        <v>0.2251</v>
+      </c>
+      <c r="X18">
+        <v>0.2228</v>
+      </c>
+      <c r="Y18">
+        <v>0.9945</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2457,8 +2490,23 @@
       <c r="AC18" t="s">
         <v>44</v>
       </c>
+      <c r="AD18">
+        <v>3.59</v>
+      </c>
       <c r="AE18" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF18">
+        <v>0.16</v>
+      </c>
+      <c r="AG18">
+        <v>0.9034</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>3.59</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2466,19 +2514,10 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
         <v>76</v>
-      </c>
-      <c r="C19">
-        <v>5.5</v>
-      </c>
-      <c r="D19">
-        <v>127</v>
-      </c>
-      <c r="E19">
-        <v>-140</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
       </c>
       <c r="G19">
         <v>823671</v>
@@ -2487,7 +2526,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2496,46 +2535,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>0.2472</v>
+        <v>0.2968</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="P19">
-        <v>4.31</v>
+        <v>4.13</v>
       </c>
       <c r="Q19">
-        <v>0.3028</v>
+        <v>0.3077</v>
       </c>
       <c r="R19">
-        <v>0.353</v>
+        <v>0.394</v>
       </c>
       <c r="S19" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T19">
-        <v>0.183</v>
+        <v>0.1962</v>
       </c>
       <c r="U19">
-        <v>0.1849</v>
+        <v>0.1989</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2364</v>
+        <v>0.2226</v>
       </c>
       <c r="X19">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y19">
-        <v>0.9607</v>
+        <v>0.9878</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2544,22 +2583,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.75</v>
+        <v>6.47</v>
       </c>
       <c r="AE19" t="s">
         <v>47</v>
       </c>
       <c r="AF19">
-        <v>0.2668</v>
+        <v>0.3011</v>
       </c>
       <c r="AG19">
-        <v>0.8328</v>
+        <v>0.8807</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.75</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2570,25 +2609,25 @@
         <v>77</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D20">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E20">
-        <v>-144</v>
+        <v>-140</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G20">
-        <v>824884</v>
+        <v>823671</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2600,43 +2639,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.1712</v>
+        <v>0.2472</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="P20">
-        <v>4.12</v>
+        <v>4.31</v>
       </c>
       <c r="Q20">
-        <v>0.1719</v>
+        <v>0.3028</v>
       </c>
       <c r="R20">
-        <v>0.39</v>
+        <v>0.353</v>
       </c>
       <c r="S20" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T20">
-        <v>0.2321</v>
+        <v>0.183</v>
       </c>
       <c r="U20">
-        <v>0.2244</v>
+        <v>0.1849</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2086</v>
+        <v>0.2364</v>
       </c>
       <c r="X20">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y20">
-        <v>0.9944</v>
+        <v>0.9607</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2645,22 +2684,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.43</v>
+        <v>4.68</v>
       </c>
       <c r="AE20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.1715</v>
+        <v>0.2668</v>
       </c>
       <c r="AG20">
-        <v>1.056</v>
+        <v>0.8214</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.43</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2668,28 +2707,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21">
+        <v>5.5</v>
+      </c>
+      <c r="D21">
+        <v>112</v>
+      </c>
+      <c r="E21">
+        <v>-123</v>
+      </c>
+      <c r="F21" t="s">
         <v>79</v>
       </c>
-      <c r="C21">
-        <v>3.5</v>
-      </c>
-      <c r="D21">
-        <v>-137</v>
-      </c>
-      <c r="E21">
-        <v>115</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
-      </c>
       <c r="G21">
-        <v>824884</v>
+        <v>823347</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2701,43 +2740,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.193</v>
+        <v>0.2157</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="P21">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="Q21">
-        <v>0.1622</v>
+        <v>0.1953</v>
       </c>
       <c r="R21">
-        <v>0.357</v>
+        <v>0.39</v>
       </c>
       <c r="S21" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T21">
-        <v>0.1764</v>
+        <v>0.2155</v>
       </c>
       <c r="U21">
-        <v>0.1763</v>
+        <v>0.2394</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.1991</v>
+        <v>0.2352</v>
       </c>
       <c r="X21">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y21">
-        <v>0.9055</v>
+        <v>1.0279</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2746,22 +2785,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>2.83</v>
+        <v>4.79</v>
       </c>
       <c r="AE21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.182</v>
+        <v>0.2077</v>
       </c>
       <c r="AG21">
-        <v>0.8028</v>
+        <v>0.9674</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>2.83</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2772,25 +2811,25 @@
         <v>80</v>
       </c>
       <c r="C22">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="D22">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="E22">
-        <v>-103</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G22">
-        <v>823914</v>
+        <v>823347</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2802,43 +2841,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.4056</v>
+        <v>0.261</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P22">
-        <v>3.78</v>
+        <v>4.22</v>
       </c>
       <c r="Q22">
-        <v>0.4528</v>
+        <v>0.2476</v>
       </c>
       <c r="R22">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="S22" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T22">
-        <v>0.2838</v>
+        <v>0.1992</v>
       </c>
       <c r="U22">
-        <v>0.2206</v>
+        <v>0.1889</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2072</v>
+        <v>0.2167</v>
       </c>
       <c r="X22">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y22">
-        <v>1.0014</v>
+        <v>0.9737</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2847,22 +2886,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>12.47</v>
+        <v>4.27</v>
       </c>
       <c r="AE22" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.4219</v>
+        <v>0.2564</v>
       </c>
       <c r="AG22">
-        <v>1.2912</v>
+        <v>0.8939</v>
       </c>
       <c r="AH22">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>11.67</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2870,28 +2909,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23">
+        <v>4.5</v>
+      </c>
+      <c r="D23">
+        <v>117</v>
+      </c>
+      <c r="E23">
+        <v>-144</v>
+      </c>
+      <c r="F23" t="s">
         <v>82</v>
       </c>
-      <c r="C23">
-        <v>5.5</v>
-      </c>
-      <c r="D23">
-        <v>125</v>
-      </c>
-      <c r="E23">
-        <v>-150</v>
-      </c>
-      <c r="F23" t="s">
-        <v>81</v>
-      </c>
       <c r="G23">
-        <v>823914</v>
+        <v>824884</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2903,43 +2942,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1911</v>
+        <v>0.1712</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P23">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="Q23">
-        <v>0.2479</v>
+        <v>0.1719</v>
       </c>
       <c r="R23">
-        <v>0.377</v>
+        <v>0.39</v>
       </c>
       <c r="S23" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T23">
-        <v>0.2056</v>
+        <v>0.2321</v>
       </c>
       <c r="U23">
-        <v>0.2348</v>
+        <v>0.2244</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2192</v>
+        <v>0.2086</v>
       </c>
       <c r="X23">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y23">
-        <v>0.9938</v>
+        <v>0.9944</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2948,22 +2987,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.95</v>
+        <v>4.37</v>
       </c>
       <c r="AE23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2125</v>
+        <v>0.1715</v>
       </c>
       <c r="AG23">
-        <v>0.9355</v>
+        <v>1.0417</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.95</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2974,25 +3013,25 @@
         <v>83</v>
       </c>
       <c r="C24">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D24">
-        <v>112</v>
+        <v>-137</v>
       </c>
       <c r="E24">
-        <v>-123</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24">
-        <v>823347</v>
+        <v>824884</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3004,43 +3043,43 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2157</v>
+        <v>0.193</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="P24">
-        <v>4.06</v>
+        <v>4.27</v>
       </c>
       <c r="Q24">
-        <v>0.1953</v>
+        <v>0.1622</v>
       </c>
       <c r="R24">
-        <v>0.39</v>
+        <v>0.357</v>
       </c>
       <c r="S24" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T24">
-        <v>0.2155</v>
+        <v>0.1764</v>
       </c>
       <c r="U24">
-        <v>0.2394</v>
+        <v>0.1763</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2352</v>
+        <v>0.1991</v>
       </c>
       <c r="X24">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y24">
-        <v>1.0279</v>
+        <v>0.9055</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3049,22 +3088,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.85</v>
+        <v>2.79</v>
       </c>
       <c r="AE24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2077</v>
+        <v>0.182</v>
       </c>
       <c r="AG24">
-        <v>0.9808</v>
+        <v>0.7919</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.85</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3072,28 +3111,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25">
+        <v>8.5</v>
+      </c>
+      <c r="D25">
+        <v>-118</v>
+      </c>
+      <c r="E25">
+        <v>-103</v>
+      </c>
+      <c r="F25" t="s">
         <v>85</v>
       </c>
-      <c r="C25">
-        <v>4.5</v>
-      </c>
-      <c r="D25">
-        <v>-120</v>
-      </c>
-      <c r="E25">
-        <v>113</v>
-      </c>
-      <c r="F25" t="s">
-        <v>84</v>
-      </c>
       <c r="G25">
-        <v>823347</v>
+        <v>823914</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3105,43 +3144,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.261</v>
+        <v>0.4056</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P25">
-        <v>4.22</v>
+        <v>3.78</v>
       </c>
       <c r="Q25">
-        <v>0.2476</v>
+        <v>0.4528</v>
       </c>
       <c r="R25">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="S25" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T25">
-        <v>0.1992</v>
+        <v>0.2838</v>
       </c>
       <c r="U25">
-        <v>0.1889</v>
+        <v>0.2206</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2167</v>
+        <v>0.2072</v>
       </c>
       <c r="X25">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y25">
-        <v>0.9737</v>
+        <v>1.0014</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3150,22 +3189,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.33</v>
+        <v>12.3</v>
       </c>
       <c r="AE25" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AF25">
-        <v>0.2564</v>
+        <v>0.4219</v>
       </c>
       <c r="AG25">
-        <v>0.9062</v>
+        <v>1.2737</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM25">
-        <v>4.33</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3176,25 +3215,25 @@
         <v>86</v>
       </c>
       <c r="C26">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E26">
-        <v>-137</v>
+        <v>-150</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G26">
-        <v>823990</v>
+        <v>823914</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3206,43 +3245,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2816</v>
+        <v>0.1911</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="P26">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="Q26">
-        <v>0.3235</v>
+        <v>0.2479</v>
       </c>
       <c r="R26">
-        <v>0.338</v>
+        <v>0.377</v>
       </c>
       <c r="S26" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T26">
-        <v>0.201</v>
+        <v>0.2056</v>
       </c>
       <c r="U26">
-        <v>0.2039</v>
+        <v>0.2348</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2145</v>
+        <v>0.2192</v>
       </c>
       <c r="X26">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y26">
-        <v>0.9609</v>
+        <v>0.9938</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3251,22 +3290,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>4.88</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.2958</v>
+        <v>0.2125</v>
       </c>
       <c r="AG26">
-        <v>0.9146</v>
+        <v>0.9228</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>6</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3274,7 +3313,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3286,7 +3325,7 @@
         <v>-150</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>823990</v>
@@ -3325,7 +3364,7 @@
         <v>0.359</v>
       </c>
       <c r="S27" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T27">
         <v>0.2683</v>
@@ -3340,7 +3379,7 @@
         <v>0.2507</v>
       </c>
       <c r="X27">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y27">
         <v>1.0431</v>
@@ -3352,22 +3391,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="AE27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF27">
         <v>0.1277</v>
       </c>
       <c r="AG27">
-        <v>1.2208</v>
+        <v>1.2042</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3381,22 +3420,22 @@
         <v>6.5</v>
       </c>
       <c r="D28">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="E28">
-        <v>-148</v>
+        <v>-137</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G28">
-        <v>824966</v>
+        <v>823990</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3408,43 +3447,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2614</v>
+        <v>0.2816</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="P28">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="Q28">
-        <v>0.2787</v>
+        <v>0.3235</v>
       </c>
       <c r="R28">
-        <v>0.379</v>
+        <v>0.338</v>
       </c>
       <c r="S28" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T28">
-        <v>0.2569</v>
+        <v>0.201</v>
       </c>
       <c r="U28">
-        <v>0.2251</v>
+        <v>0.2039</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>0.2494</v>
+        <v>0.2145</v>
       </c>
       <c r="X28">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y28">
-        <v>1.0317</v>
+        <v>0.9609</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3453,22 +3492,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>7.37</v>
+        <v>5.92</v>
       </c>
       <c r="AE28" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.268</v>
+        <v>0.2958</v>
       </c>
       <c r="AG28">
-        <v>1.169</v>
+        <v>0.9021</v>
       </c>
       <c r="AH28">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>6.57</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3476,34 +3515,76 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <v>6.5</v>
+      </c>
+      <c r="D29">
+        <v>128</v>
+      </c>
+      <c r="E29">
+        <v>-148</v>
+      </c>
+      <c r="F29" t="s">
         <v>91</v>
       </c>
-      <c r="C29">
-        <v>4.5</v>
-      </c>
-      <c r="D29">
-        <v>-105</v>
-      </c>
-      <c r="E29">
-        <v>-115</v>
-      </c>
-      <c r="F29" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" t="s">
-        <v>44</v>
+      <c r="G29">
+        <v>824966</v>
       </c>
       <c r="H29" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I29">
+        <v>5.4</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
       </c>
       <c r="L29">
         <v>6</v>
       </c>
+      <c r="M29">
+        <v>0.2614</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29">
+        <v>122</v>
+      </c>
+      <c r="P29">
+        <v>4.25</v>
+      </c>
+      <c r="Q29">
+        <v>0.2787</v>
+      </c>
+      <c r="R29">
+        <v>0.379</v>
+      </c>
       <c r="S29" t="s">
-        <v>44</v>
-      </c>
-      <c r="V29" t="s">
-        <v>44</v>
+        <v>58</v>
+      </c>
+      <c r="T29">
+        <v>0.2569</v>
+      </c>
+      <c r="U29">
+        <v>0.2251</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.2494</v>
+      </c>
+      <c r="X29">
+        <v>0.2228</v>
+      </c>
+      <c r="Y29">
+        <v>1.0317</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3511,8 +3592,23 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
+      <c r="AD29">
+        <v>7.27</v>
+      </c>
       <c r="AE29" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AF29">
+        <v>0.268</v>
+      </c>
+      <c r="AG29">
+        <v>1.1531</v>
+      </c>
+      <c r="AH29">
+        <v>-0.77</v>
+      </c>
+      <c r="AM29">
+        <v>6.5</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3523,19 +3619,19 @@
         <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="G30">
-        <v>822775</v>
+        <v>824966</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I30">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -3544,43 +3640,43 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.2298</v>
+        <v>0.2106</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="P30">
-        <v>4.07</v>
+        <v>4.19</v>
       </c>
       <c r="Q30">
-        <v>0.2083</v>
+        <v>0.2174</v>
       </c>
       <c r="R30">
-        <v>0.107</v>
+        <v>0.365</v>
       </c>
       <c r="S30" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T30">
-        <v>0.2725</v>
+        <v>0.2141</v>
       </c>
       <c r="U30">
-        <v>0.2683</v>
+        <v>0.2308</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2434</v>
+        <v>0.2207</v>
       </c>
       <c r="X30">
-        <v>0.2198</v>
+        <v>0.2228</v>
       </c>
       <c r="Y30">
-        <v>1.002</v>
+        <v>1.0405</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3589,22 +3685,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>1.31</v>
+        <v>4.86</v>
       </c>
       <c r="AE30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF30">
-        <v>0.2275</v>
+        <v>0.2131</v>
       </c>
       <c r="AG30">
-        <v>1.2399</v>
+        <v>0.9608</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.31</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3614,65 +3710,32 @@
       <c r="B31" t="s">
         <v>93</v>
       </c>
+      <c r="C31">
+        <v>6.5</v>
+      </c>
+      <c r="D31">
+        <v>-103</v>
+      </c>
+      <c r="E31">
+        <v>-120</v>
+      </c>
       <c r="F31" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31">
-        <v>823671</v>
+        <v>76</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31">
+        <v>44</v>
+      </c>
+      <c r="L31">
         <v>6</v>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.2968</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>130</v>
-      </c>
-      <c r="P31">
-        <v>4.13</v>
-      </c>
-      <c r="Q31">
-        <v>0.3077</v>
-      </c>
-      <c r="R31">
-        <v>0.394</v>
-      </c>
       <c r="S31" t="s">
-        <v>50</v>
-      </c>
-      <c r="T31">
-        <v>0.1962</v>
-      </c>
-      <c r="U31">
-        <v>0.1989</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.2226</v>
-      </c>
-      <c r="X31">
-        <v>0.2198</v>
-      </c>
-      <c r="Y31">
-        <v>0.9878</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3680,23 +3743,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>6.56</v>
-      </c>
       <c r="AE31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF31">
-        <v>0.3011</v>
-      </c>
-      <c r="AG31">
-        <v>0.8929</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>6.56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3706,65 +3754,32 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>-105</v>
+      </c>
+      <c r="E32">
+        <v>-115</v>
+      </c>
       <c r="F32" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32">
-        <v>824966</v>
+        <v>91</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
-        <v>5.4</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2106</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>115</v>
-      </c>
-      <c r="P32">
-        <v>4.19</v>
-      </c>
-      <c r="Q32">
-        <v>0.2174</v>
-      </c>
-      <c r="R32">
-        <v>0.365</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>50</v>
-      </c>
-      <c r="T32">
-        <v>0.2141</v>
-      </c>
-      <c r="U32">
-        <v>0.2308</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2207</v>
-      </c>
-      <c r="X32">
-        <v>0.2198</v>
-      </c>
-      <c r="Y32">
-        <v>1.0405</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3772,23 +3787,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>4.92</v>
-      </c>
       <c r="AE32" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF32">
-        <v>0.2131</v>
-      </c>
-      <c r="AG32">
-        <v>0.974</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>4.92</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-15.xlsx
+++ b/data/k-props/2026-08-15.xlsx
@@ -154,73 +154,73 @@
     <t>Troy Melton</t>
   </si>
   <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Braydon Fisher</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Michael Lorenzen</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ New York Mets</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Ian Seymour</t>
+  </si>
+  <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Braydon Fisher</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Michael Lorenzen</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Brady Singer</t>
   </si>
   <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ New York Mets</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Ian Seymour</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Brady Singer</t>
   </si>
   <si>
     <t>Joey Cantillo</t>
@@ -839,22 +839,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.1811</v>
+        <v>0.1815</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P2">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="Q2">
-        <v>0.1983</v>
+        <v>0.1864</v>
       </c>
       <c r="R2">
-        <v>0.367</v>
+        <v>0.371</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -872,7 +872,7 @@
         <v>0.2277</v>
       </c>
       <c r="X2">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y2">
         <v>0.9736</v>
@@ -884,22 +884,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1874</v>
+        <v>0.1833</v>
       </c>
       <c r="AG2">
-        <v>0.822</v>
+        <v>0.8152</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -928,7 +928,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -940,22 +940,22 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.2248</v>
+        <v>0.2219</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P3">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
-        <v>0.2373</v>
+        <v>0.1966</v>
       </c>
       <c r="R3">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -973,7 +973,7 @@
         <v>0.2369</v>
       </c>
       <c r="X3">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y3">
         <v>1.0768</v>
@@ -985,22 +985,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>6.26</v>
+        <v>5.73</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2294</v>
+        <v>0.2125</v>
       </c>
       <c r="AG3">
-        <v>1.0738</v>
+        <v>1.065</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>6.26</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1008,7 +1008,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -1020,7 +1020,7 @@
         <v>-125</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>824644</v>
@@ -1029,7 +1029,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="P4">
         <v>4.07</v>
       </c>
       <c r="Q4">
-        <v>0.1696</v>
+        <v>0.1667</v>
       </c>
       <c r="R4">
-        <v>0.359</v>
+        <v>0.31</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1074,7 +1074,7 @@
         <v>0.2174</v>
       </c>
       <c r="X4">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y4">
         <v>0.9668</v>
@@ -1086,22 +1086,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1671</v>
+        <v>0.166</v>
       </c>
       <c r="AG4">
-        <v>1.1106</v>
+        <v>1.1015</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1109,7 +1109,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1121,7 +1121,7 @@
         <v>-106</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>824644</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1142,22 +1142,22 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2006</v>
+        <v>0.2012</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="P5">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="Q5">
-        <v>0.1429</v>
+        <v>0.1405</v>
       </c>
       <c r="R5">
-        <v>0.399</v>
+        <v>0.377</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1175,7 +1175,7 @@
         <v>0.1835</v>
       </c>
       <c r="X5">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y5">
         <v>0.9265</v>
@@ -1187,22 +1187,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1775</v>
+        <v>0.1783</v>
       </c>
       <c r="AG5">
-        <v>1.137</v>
+        <v>1.1277</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1210,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>6.5</v>
@@ -1222,7 +1222,7 @@
         <v>-138</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>822775</v>
@@ -1276,7 +1276,7 @@
         <v>0.1893</v>
       </c>
       <c r="X6">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y6">
         <v>1.0898</v>
@@ -1288,22 +1288,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>9.58</v>
+        <v>9.5</v>
       </c>
       <c r="AE6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF6">
         <v>0.348</v>
       </c>
       <c r="AG6">
-        <v>1.0905</v>
+        <v>1.0816</v>
       </c>
       <c r="AH6">
         <v>-0.77</v>
       </c>
       <c r="AM6">
-        <v>8.81</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,16 +1311,16 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>822775</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I7">
         <v>1.1</v>
@@ -1368,7 +1368,7 @@
         <v>0.2434</v>
       </c>
       <c r="X7">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y7">
         <v>1.0475</v>
@@ -1380,7 +1380,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1389,13 +1389,13 @@
         <v>0.2275</v>
       </c>
       <c r="AG7">
-        <v>1.1419</v>
+        <v>1.1325</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1403,7 +1403,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1415,7 +1415,7 @@
         <v>-140</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>823184</v>
@@ -1454,25 +1454,25 @@
         <v>0.338</v>
       </c>
       <c r="S8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2156</v>
+        <v>0.243</v>
       </c>
       <c r="U8">
-        <v>0.2174</v>
+        <v>0.216</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>0.2021</v>
       </c>
       <c r="X8">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y8">
-        <v>0.9683</v>
+        <v>0.9007</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1481,7 +1481,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1490,13 +1490,13 @@
         <v>0.1286</v>
       </c>
       <c r="AG8">
-        <v>0.9678</v>
+        <v>1.0816</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1504,7 +1504,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1516,7 +1516,7 @@
         <v>-115</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>823184</v>
@@ -1555,13 +1555,13 @@
         <v>0.387</v>
       </c>
       <c r="S9" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.228</v>
+        <v>0.2245</v>
       </c>
       <c r="U9">
-        <v>0.2254</v>
+        <v>0.2071</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1570,10 +1570,10 @@
         <v>0.2164</v>
       </c>
       <c r="X9">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y9">
-        <v>1.0137</v>
+        <v>0.9947</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1582,7 +1582,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5</v>
+        <v>4.79</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1591,13 +1591,13 @@
         <v>0.188</v>
       </c>
       <c r="AG9">
-        <v>1.0232</v>
+        <v>0.9992</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1605,7 +1605,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1617,13 +1617,13 @@
         <v>-151</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>823588</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10">
         <v>2.5</v>
@@ -1656,13 +1656,13 @@
         <v>0.099</v>
       </c>
       <c r="S10" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2411</v>
+        <v>0.2573</v>
       </c>
       <c r="U10">
-        <v>0.2383</v>
+        <v>0.2469</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1671,10 +1671,10 @@
         <v>0.2248</v>
       </c>
       <c r="X10">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y10">
-        <v>0.9942</v>
+        <v>0.9929</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1683,7 +1683,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1692,13 +1692,13 @@
         <v>0.2151</v>
       </c>
       <c r="AG10">
-        <v>1.0823</v>
+        <v>1.1453</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1706,7 +1706,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1718,7 +1718,7 @@
         <v>118</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>823588</v>
@@ -1757,13 +1757,13 @@
         <v>0.385</v>
       </c>
       <c r="S11" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2088</v>
+        <v>0.2143</v>
       </c>
       <c r="U11">
-        <v>0.2149</v>
+        <v>0.2183</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1772,10 +1772,10 @@
         <v>0.2345</v>
       </c>
       <c r="X11">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y11">
-        <v>0.9877</v>
+        <v>1.0233</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1784,7 +1784,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1793,13 +1793,13 @@
         <v>0.2421</v>
       </c>
       <c r="AG11">
-        <v>0.9374</v>
+        <v>0.9541</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1807,7 +1807,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1819,7 +1819,7 @@
         <v>-109</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>822941</v>
@@ -1858,13 +1858,13 @@
         <v>0.346</v>
       </c>
       <c r="S12" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1806</v>
+        <v>0.1815</v>
       </c>
       <c r="U12">
-        <v>0.1761</v>
+        <v>0.1767</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1873,10 +1873,10 @@
         <v>0.1896</v>
       </c>
       <c r="X12">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y12">
-        <v>0.8948</v>
+        <v>0.88</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1885,7 +1885,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1894,13 +1894,13 @@
         <v>0.2132</v>
       </c>
       <c r="AG12">
-        <v>0.8107</v>
+        <v>0.8081</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1908,7 +1908,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>6.5</v>
@@ -1920,7 +1920,7 @@
         <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>822941</v>
@@ -1959,25 +1959,25 @@
         <v>0.34</v>
       </c>
       <c r="S13" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2888</v>
+        <v>0.2644</v>
       </c>
       <c r="U13">
-        <v>0.2554</v>
+        <v>0.2523</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>0.2573</v>
       </c>
       <c r="X13">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y13">
-        <v>1.0111</v>
+        <v>1.0233</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1986,22 +1986,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.41</v>
+        <v>6.81</v>
       </c>
       <c r="AE13" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="AF13">
         <v>0.3031</v>
       </c>
       <c r="AG13">
-        <v>1.2964</v>
+        <v>1.1772</v>
       </c>
       <c r="AH13">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>6.64</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2009,7 +2009,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2021,13 +2021,13 @@
         <v>-104</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>824480</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -2060,13 +2060,13 @@
         <v>0.32</v>
       </c>
       <c r="S14" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2482</v>
+        <v>0.2706</v>
       </c>
       <c r="U14">
-        <v>0.2609</v>
+        <v>0.2672</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -2075,10 +2075,10 @@
         <v>0.2532</v>
       </c>
       <c r="X14">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y14">
-        <v>1.0366</v>
+        <v>1.076</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2087,7 +2087,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.97</v>
+        <v>4.46</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2096,13 +2096,13 @@
         <v>0.1966</v>
       </c>
       <c r="AG14">
-        <v>1.114</v>
+        <v>1.2045</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.97</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2110,7 +2110,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2122,7 +2122,7 @@
         <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>824480</v>
@@ -2161,7 +2161,7 @@
         <v>0.39</v>
       </c>
       <c r="S15" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T15">
         <v>0.2453</v>
@@ -2176,7 +2176,7 @@
         <v>0.2115</v>
       </c>
       <c r="X15">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y15">
         <v>0.96</v>
@@ -2188,7 +2188,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2197,13 +2197,13 @@
         <v>0.1882</v>
       </c>
       <c r="AG15">
-        <v>1.101</v>
+        <v>1.092</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2262,7 +2262,7 @@
         <v>0.315</v>
       </c>
       <c r="S16" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T16">
         <v>0.1514</v>
@@ -2277,7 +2277,7 @@
         <v>0.2154</v>
       </c>
       <c r="X16">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y16">
         <v>0.9934</v>
@@ -2289,7 +2289,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2298,13 +2298,13 @@
         <v>0.2657</v>
       </c>
       <c r="AG16">
-        <v>0.6795</v>
+        <v>0.6739</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2363,7 +2363,7 @@
         <v>0.346</v>
       </c>
       <c r="S17" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T17">
         <v>0.2068</v>
@@ -2378,7 +2378,7 @@
         <v>0.2154</v>
       </c>
       <c r="X17">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y17">
         <v>0.9979</v>
@@ -2390,7 +2390,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2399,13 +2399,13 @@
         <v>0.2102</v>
       </c>
       <c r="AG17">
-        <v>0.9281</v>
+        <v>0.9205</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2464,7 +2464,7 @@
         <v>0.273</v>
       </c>
       <c r="S18" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T18">
         <v>0.2013</v>
@@ -2479,7 +2479,7 @@
         <v>0.2251</v>
       </c>
       <c r="X18">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y18">
         <v>0.9945</v>
@@ -2491,7 +2491,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2500,13 +2500,13 @@
         <v>0.16</v>
       </c>
       <c r="AG18">
-        <v>0.9034</v>
+        <v>0.896</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2556,13 +2556,13 @@
         <v>0.394</v>
       </c>
       <c r="S19" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.1962</v>
+        <v>0.2046</v>
       </c>
       <c r="U19">
-        <v>0.1989</v>
+        <v>0.1916</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2571,10 +2571,10 @@
         <v>0.2226</v>
       </c>
       <c r="X19">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y19">
-        <v>0.9878</v>
+        <v>0.9625</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2583,22 +2583,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.47</v>
+        <v>6.52</v>
       </c>
       <c r="AE19" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF19">
         <v>0.3011</v>
       </c>
       <c r="AG19">
-        <v>0.8807</v>
+        <v>0.9108</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>6.47</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2657,7 +2657,7 @@
         <v>0.353</v>
       </c>
       <c r="S20" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T20">
         <v>0.183</v>
@@ -2672,7 +2672,7 @@
         <v>0.2364</v>
       </c>
       <c r="X20">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y20">
         <v>0.9607</v>
@@ -2684,7 +2684,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2693,13 +2693,13 @@
         <v>0.2668</v>
       </c>
       <c r="AG20">
-        <v>0.8214</v>
+        <v>0.8147</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2758,7 +2758,7 @@
         <v>0.39</v>
       </c>
       <c r="S21" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T21">
         <v>0.2155</v>
@@ -2773,7 +2773,7 @@
         <v>0.2352</v>
       </c>
       <c r="X21">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y21">
         <v>1.0279</v>
@@ -2785,7 +2785,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2794,13 +2794,13 @@
         <v>0.2077</v>
       </c>
       <c r="AG21">
-        <v>0.9674</v>
+        <v>0.9595</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2859,7 +2859,7 @@
         <v>0.344</v>
       </c>
       <c r="S22" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T22">
         <v>0.1992</v>
@@ -2874,7 +2874,7 @@
         <v>0.2167</v>
       </c>
       <c r="X22">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y22">
         <v>0.9737</v>
@@ -2886,7 +2886,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2895,13 +2895,13 @@
         <v>0.2564</v>
       </c>
       <c r="AG22">
-        <v>0.8939</v>
+        <v>0.8866</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2960,7 +2960,7 @@
         <v>0.39</v>
       </c>
       <c r="S23" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T23">
         <v>0.2321</v>
@@ -2975,7 +2975,7 @@
         <v>0.2086</v>
       </c>
       <c r="X23">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y23">
         <v>0.9944</v>
@@ -2987,7 +2987,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2996,13 +2996,13 @@
         <v>0.1715</v>
       </c>
       <c r="AG23">
-        <v>1.0417</v>
+        <v>1.0331</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3061,13 +3061,13 @@
         <v>0.357</v>
       </c>
       <c r="S24" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.1764</v>
+        <v>0.1789</v>
       </c>
       <c r="U24">
-        <v>0.1763</v>
+        <v>0.1783</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -3076,10 +3076,10 @@
         <v>0.1991</v>
       </c>
       <c r="X24">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y24">
-        <v>0.9055</v>
+        <v>0.88</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3088,7 +3088,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3097,13 +3097,13 @@
         <v>0.182</v>
       </c>
       <c r="AG24">
-        <v>0.7919</v>
+        <v>0.7963</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3162,7 +3162,7 @@
         <v>0.346</v>
       </c>
       <c r="S25" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T25">
         <v>0.2838</v>
@@ -3177,7 +3177,7 @@
         <v>0.2072</v>
       </c>
       <c r="X25">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y25">
         <v>1.0014</v>
@@ -3189,22 +3189,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="AE25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF25">
         <v>0.4219</v>
       </c>
       <c r="AG25">
-        <v>1.2737</v>
+        <v>1.2632</v>
       </c>
       <c r="AH25">
         <v>-0.77</v>
       </c>
       <c r="AM25">
-        <v>11.53</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3263,7 +3263,7 @@
         <v>0.377</v>
       </c>
       <c r="S26" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T26">
         <v>0.2056</v>
@@ -3278,7 +3278,7 @@
         <v>0.2192</v>
       </c>
       <c r="X26">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y26">
         <v>0.9938</v>
@@ -3290,7 +3290,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3299,13 +3299,13 @@
         <v>0.2125</v>
       </c>
       <c r="AG26">
-        <v>0.9228</v>
+        <v>0.9152</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3364,7 +3364,7 @@
         <v>0.359</v>
       </c>
       <c r="S27" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T27">
         <v>0.2683</v>
@@ -3379,7 +3379,7 @@
         <v>0.2507</v>
       </c>
       <c r="X27">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y27">
         <v>1.0431</v>
@@ -3391,7 +3391,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3400,13 +3400,13 @@
         <v>0.1277</v>
       </c>
       <c r="AG27">
-        <v>1.2042</v>
+        <v>1.1943</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3465,7 +3465,7 @@
         <v>0.338</v>
       </c>
       <c r="S28" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T28">
         <v>0.201</v>
@@ -3480,7 +3480,7 @@
         <v>0.2145</v>
       </c>
       <c r="X28">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y28">
         <v>0.9609</v>
@@ -3492,7 +3492,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3501,13 +3501,13 @@
         <v>0.2958</v>
       </c>
       <c r="AG28">
-        <v>0.9021</v>
+        <v>0.8947</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3566,7 +3566,7 @@
         <v>0.379</v>
       </c>
       <c r="S29" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T29">
         <v>0.2569</v>
@@ -3581,7 +3581,7 @@
         <v>0.2494</v>
       </c>
       <c r="X29">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y29">
         <v>1.0317</v>
@@ -3593,22 +3593,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>7.27</v>
+        <v>7.21</v>
       </c>
       <c r="AE29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF29">
         <v>0.268</v>
       </c>
       <c r="AG29">
-        <v>1.1531</v>
+        <v>1.1437</v>
       </c>
       <c r="AH29">
         <v>-0.77</v>
       </c>
       <c r="AM29">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>0.365</v>
       </c>
       <c r="S30" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T30">
         <v>0.2141</v>
@@ -3673,7 +3673,7 @@
         <v>0.2207</v>
       </c>
       <c r="X30">
-        <v>0.2228</v>
+        <v>0.2246</v>
       </c>
       <c r="Y30">
         <v>1.0405</v>
@@ -3685,7 +3685,7 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
@@ -3694,13 +3694,13 @@
         <v>0.2131</v>
       </c>
       <c r="AG30">
-        <v>0.9608</v>
+        <v>0.9529</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-15.xlsx
+++ b/data/k-props/2026-08-15.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -133,24 +133,147 @@
     <t>08/15/2026</t>
   </si>
   <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ New York Mets</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>Ian Seymour</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Brady Singer</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Justin Wrobleski</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
+    <t>JT Ginn</t>
+  </si>
+  <si>
     <t>Anthony Kay</t>
   </si>
   <si>
     <t>Chicago White Sox @ Detroit Tigers</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Troy Melton</t>
   </si>
   <si>
@@ -163,139 +286,19 @@
     <t>Matthew Boyd</t>
   </si>
   <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
     <t>Braydon Fisher</t>
   </si>
   <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
     <t>Michael Lorenzen</t>
   </si>
   <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ New York Mets</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Ian Seymour</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Brady Singer</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Emerson Hancock</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
+    <t>Wandy Peralta</t>
   </si>
   <si>
     <t>Jesús Luzardo</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Justin Wrobleski</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
-  </si>
-  <si>
     <t>J.T. Ginn</t>
-  </si>
-  <si>
-    <t>Jesus Luzardo</t>
-  </si>
-  <si>
-    <t>JT Ginn</t>
   </si>
 </sst>
 </file>
@@ -676,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -809,25 +812,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D2">
-        <v>115</v>
+        <v>-140</v>
       </c>
       <c r="E2">
-        <v>-129</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>824239</v>
+        <v>822775</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -836,46 +839,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0.1815</v>
+        <v>0.3143</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="P2">
-        <v>4.46</v>
+        <v>3.96</v>
       </c>
       <c r="Q2">
-        <v>0.1864</v>
+        <v>0.3905</v>
       </c>
       <c r="R2">
-        <v>0.371</v>
+        <v>0.344</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1831</v>
+        <v>0.243</v>
       </c>
       <c r="U2">
-        <v>0.2045</v>
+        <v>0.2233</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2277</v>
+        <v>0.1893</v>
       </c>
       <c r="X2">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y2">
-        <v>0.9736</v>
+        <v>1.0898</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -884,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.22</v>
+        <v>9.24</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1833</v>
+        <v>0.3405</v>
       </c>
       <c r="AG2">
-        <v>0.8152</v>
+        <v>1.0877</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM2">
-        <v>3.22</v>
+        <v>8.47</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -913,22 +916,22 @@
         <v>5.5</v>
       </c>
       <c r="D3">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E3">
-        <v>-128</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>824239</v>
+        <v>823184</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -937,46 +940,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>0.2219</v>
+        <v>0.1922</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="P3">
-        <v>3.9</v>
+        <v>4.04</v>
       </c>
       <c r="Q3">
-        <v>0.1966</v>
+        <v>0.1845</v>
       </c>
       <c r="R3">
-        <v>0.369</v>
+        <v>0.34</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2392</v>
+        <v>0.2245</v>
       </c>
       <c r="U3">
-        <v>0.2457</v>
+        <v>0.2071</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2369</v>
+        <v>0.2164</v>
       </c>
       <c r="X3">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y3">
-        <v>1.0768</v>
+        <v>0.9947</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -985,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.73</v>
+        <v>4.66</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF3">
-        <v>0.2125</v>
+        <v>0.1896</v>
       </c>
       <c r="AG3">
-        <v>1.065</v>
+        <v>1.0049</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.73</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1008,76 +1011,76 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E4">
-        <v>-125</v>
+        <v>-164</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>824644</v>
+        <v>823588</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>0.1657</v>
+        <v>0.2121</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>4.07</v>
+        <v>4.28</v>
       </c>
       <c r="Q4">
-        <v>0.1667</v>
+        <v>0.2174</v>
       </c>
       <c r="R4">
-        <v>0.31</v>
+        <v>0.103</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2474</v>
+        <v>0.2573</v>
       </c>
       <c r="U4">
-        <v>0.2364</v>
+        <v>0.2469</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2174</v>
+        <v>0.2248</v>
       </c>
       <c r="X4">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y4">
-        <v>0.9668</v>
+        <v>0.9929</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1086,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.82</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF4">
-        <v>0.166</v>
+        <v>0.2127</v>
       </c>
       <c r="AG4">
-        <v>1.1015</v>
+        <v>1.1518</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.82</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1109,28 +1112,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5">
-        <v>-106</v>
+        <v>-150</v>
       </c>
       <c r="E5">
-        <v>-106</v>
+        <v>122</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
-        <v>824644</v>
+        <v>823588</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1142,43 +1145,43 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2012</v>
+        <v>0.2363</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="P5">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="Q5">
-        <v>0.1405</v>
+        <v>0.2596</v>
       </c>
       <c r="R5">
-        <v>0.377</v>
+        <v>0.342</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2533</v>
+        <v>0.2143</v>
       </c>
       <c r="U5">
-        <v>0.2142</v>
+        <v>0.2183</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>0.1835</v>
+        <v>0.2345</v>
       </c>
       <c r="X5">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y5">
-        <v>0.9265</v>
+        <v>1.0233</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1187,22 +1190,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.2</v>
+        <v>5.42</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF5">
-        <v>0.1783</v>
+        <v>0.2443</v>
       </c>
       <c r="AG5">
-        <v>1.1277</v>
+        <v>0.9595</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.2</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1210,28 +1213,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>6.5</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>-120</v>
       </c>
       <c r="E6">
-        <v>-138</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>822775</v>
+        <v>822941</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1243,43 +1246,43 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.3143</v>
+        <v>0.2842</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="P6">
-        <v>3.95</v>
+        <v>4.13</v>
       </c>
       <c r="Q6">
-        <v>0.4091</v>
+        <v>0.3398</v>
       </c>
       <c r="R6">
-        <v>0.355</v>
+        <v>0.34</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.243</v>
+        <v>0.2644</v>
       </c>
       <c r="U6">
-        <v>0.2233</v>
+        <v>0.2523</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.1893</v>
+        <v>0.2573</v>
       </c>
       <c r="X6">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y6">
-        <v>1.0898</v>
+        <v>1.0233</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1288,22 +1291,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>9.5</v>
+        <v>6.85</v>
       </c>
       <c r="AE6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF6">
-        <v>0.348</v>
+        <v>0.3031</v>
       </c>
       <c r="AG6">
-        <v>1.0816</v>
+        <v>1.1838</v>
       </c>
       <c r="AH6">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>8.73</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,67 +1314,76 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7">
+        <v>-104</v>
+      </c>
+      <c r="E7">
+        <v>-115</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>822775</v>
+        <v>822941</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>0.2298</v>
+        <v>0.2262</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="P7">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="Q7">
-        <v>0.2083</v>
+        <v>0.1887</v>
       </c>
       <c r="R7">
-        <v>0.107</v>
+        <v>0.346</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2544</v>
+        <v>0.1815</v>
       </c>
       <c r="U7">
-        <v>0.2579</v>
+        <v>0.1767</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2434</v>
+        <v>0.1896</v>
       </c>
       <c r="X7">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y7">
-        <v>1.0475</v>
+        <v>0.88</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1380,22 +1392,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF7">
-        <v>0.2275</v>
+        <v>0.2132</v>
       </c>
       <c r="AG7">
-        <v>1.1325</v>
+        <v>0.8127</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1403,28 +1415,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E8">
-        <v>-140</v>
+        <v>-135</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>823184</v>
+        <v>824480</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,43 +1448,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1492</v>
+        <v>0.1887</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="P8">
-        <v>4.8</v>
+        <v>4.43</v>
       </c>
       <c r="Q8">
-        <v>0.0882</v>
+        <v>0.1875</v>
       </c>
       <c r="R8">
-        <v>0.338</v>
+        <v>0.39</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.243</v>
+        <v>0.2698</v>
       </c>
       <c r="U8">
-        <v>0.216</v>
+        <v>0.2556</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2021</v>
+        <v>0.2115</v>
       </c>
       <c r="X8">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y8">
-        <v>0.9007</v>
+        <v>0.9392</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1481,22 +1493,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.78</v>
+        <v>4.92</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF8">
-        <v>0.1286</v>
+        <v>0.1882</v>
       </c>
       <c r="AG8">
-        <v>1.0816</v>
+        <v>1.2079</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.78</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1504,28 +1516,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>-103</v>
       </c>
       <c r="E9">
         <v>-115</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>823184</v>
+        <v>824480</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I9">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1537,43 +1549,43 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.1914</v>
+        <v>0.1991</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="P9">
-        <v>4.05</v>
+        <v>4.41</v>
       </c>
       <c r="Q9">
-        <v>0.1825</v>
+        <v>0.1915</v>
       </c>
       <c r="R9">
-        <v>0.387</v>
+        <v>0.32</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2245</v>
+        <v>0.2706</v>
       </c>
       <c r="U9">
-        <v>0.2071</v>
+        <v>0.2672</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2164</v>
+        <v>0.2532</v>
       </c>
       <c r="X9">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y9">
-        <v>0.9947</v>
+        <v>1.076</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1582,22 +1594,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.79</v>
+        <v>4.48</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF9">
-        <v>0.188</v>
+        <v>0.1966</v>
       </c>
       <c r="AG9">
-        <v>0.9992</v>
+        <v>1.2113</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.79</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1605,76 +1617,76 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E10">
-        <v>-151</v>
+        <v>-138</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10">
-        <v>823588</v>
+        <v>824400</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>0.2137</v>
+        <v>0.2529</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="P10">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="Q10">
-        <v>0.2273</v>
+        <v>0.2935</v>
       </c>
       <c r="R10">
-        <v>0.099</v>
+        <v>0.315</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2573</v>
+        <v>0.174</v>
       </c>
       <c r="U10">
-        <v>0.2469</v>
+        <v>0.1783</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2248</v>
+        <v>0.2154</v>
       </c>
       <c r="X10">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y10">
-        <v>0.9929</v>
+        <v>1.0658</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1683,22 +1695,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.6</v>
+        <v>4.61</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF10">
-        <v>0.2151</v>
+        <v>0.2657</v>
       </c>
       <c r="AG10">
-        <v>1.1453</v>
+        <v>0.7791</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.6</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1706,28 +1718,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>118</v>
+        <v>-104</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G11">
-        <v>823588</v>
+        <v>824157</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1739,43 +1751,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2335</v>
+        <v>0.2265</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="P11">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="Q11">
-        <v>0.256</v>
+        <v>0.1792</v>
       </c>
       <c r="R11">
-        <v>0.385</v>
+        <v>0.346</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2143</v>
+        <v>0.2108</v>
       </c>
       <c r="U11">
-        <v>0.2183</v>
+        <v>0.2017</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2345</v>
+        <v>0.2154</v>
       </c>
       <c r="X11">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y11">
-        <v>1.0233</v>
+        <v>0.9861</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1784,22 +1796,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.75</v>
+        <v>4.36</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF11">
-        <v>0.2421</v>
+        <v>0.2102</v>
       </c>
       <c r="AG11">
-        <v>0.9541</v>
+        <v>0.9437</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.75</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1807,28 +1819,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>-113</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>-109</v>
+        <v>-135</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12">
-        <v>822941</v>
+        <v>824157</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1840,43 +1852,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2262</v>
+        <v>0.16</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="P12">
-        <v>4.21</v>
+        <v>4.02</v>
       </c>
       <c r="Q12">
-        <v>0.1887</v>
+        <v>0.16</v>
       </c>
       <c r="R12">
-        <v>0.346</v>
+        <v>0.273</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1815</v>
+        <v>0.2032</v>
       </c>
       <c r="U12">
-        <v>0.1767</v>
+        <v>0.186</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.1896</v>
+        <v>0.2251</v>
       </c>
       <c r="X12">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y12">
-        <v>0.88</v>
+        <v>0.9867</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1885,22 +1897,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF12">
-        <v>0.2132</v>
+        <v>0.16</v>
       </c>
       <c r="AG12">
-        <v>0.8081</v>
+        <v>0.9099</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1908,76 +1920,34 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>6.5</v>
       </c>
       <c r="D13">
-        <v>-111</v>
+        <v>102</v>
       </c>
       <c r="E13">
-        <v>103</v>
+        <v>-120</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>822941</v>
+        <v>67</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13">
-        <v>4.5</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
-      <c r="M13">
-        <v>0.2842</v>
-      </c>
-      <c r="N13">
-        <v>5</v>
-      </c>
-      <c r="O13">
-        <v>103</v>
-      </c>
-      <c r="P13">
-        <v>4.13</v>
-      </c>
-      <c r="Q13">
-        <v>0.3398</v>
-      </c>
-      <c r="R13">
-        <v>0.34</v>
-      </c>
       <c r="S13" t="s">
-        <v>43</v>
-      </c>
-      <c r="T13">
-        <v>0.2644</v>
-      </c>
-      <c r="U13">
-        <v>0.2523</v>
-      </c>
-      <c r="V13">
-        <v>9</v>
-      </c>
-      <c r="W13">
-        <v>0.2573</v>
-      </c>
-      <c r="X13">
-        <v>0.2246</v>
-      </c>
-      <c r="Y13">
-        <v>1.0233</v>
+        <v>44</v>
+      </c>
+      <c r="V13" t="s">
+        <v>44</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1985,23 +1955,8 @@
       <c r="AC13" t="s">
         <v>44</v>
       </c>
-      <c r="AD13">
-        <v>6.81</v>
-      </c>
       <c r="AE13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF13">
-        <v>0.3031</v>
-      </c>
-      <c r="AG13">
-        <v>1.1772</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>6.81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2009,28 +1964,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-103</v>
+        <v>118</v>
       </c>
       <c r="E14">
-        <v>-104</v>
+        <v>-140</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
-        <v>824480</v>
+        <v>823671</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2042,43 +1997,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1991</v>
+        <v>0.2472</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="P14">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="Q14">
-        <v>0.1915</v>
+        <v>0.3028</v>
       </c>
       <c r="R14">
-        <v>0.32</v>
+        <v>0.353</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="T14">
-        <v>0.2706</v>
+        <v>0.183</v>
       </c>
       <c r="U14">
-        <v>0.2672</v>
+        <v>0.1849</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2532</v>
+        <v>0.2364</v>
       </c>
       <c r="X14">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y14">
-        <v>1.076</v>
+        <v>0.9607</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2087,22 +2042,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.46</v>
+        <v>4.67</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF14">
-        <v>0.1966</v>
+        <v>0.2668</v>
       </c>
       <c r="AG14">
-        <v>1.2045</v>
+        <v>0.8193</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.46</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2110,28 +2065,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-145</v>
+        <v>120</v>
       </c>
       <c r="E15">
-        <v>125</v>
+        <v>-149</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G15">
-        <v>824480</v>
+        <v>824884</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2143,7 +2098,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1887</v>
+        <v>0.1712</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -2152,34 +2107,34 @@
         <v>128</v>
       </c>
       <c r="P15">
-        <v>4.43</v>
+        <v>4.12</v>
       </c>
       <c r="Q15">
-        <v>0.1875</v>
+        <v>0.1719</v>
       </c>
       <c r="R15">
         <v>0.39</v>
       </c>
       <c r="S15" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2453</v>
+        <v>0.2562</v>
       </c>
       <c r="U15">
-        <v>0.2358</v>
+        <v>0.2259</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2115</v>
+        <v>0.2086</v>
       </c>
       <c r="X15">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y15">
-        <v>0.96</v>
+        <v>0.9928</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2188,22 +2143,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF15">
-        <v>0.1882</v>
+        <v>0.1715</v>
       </c>
       <c r="AG15">
-        <v>1.092</v>
+        <v>1.1471</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2211,28 +2166,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C16">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
-        <v>118</v>
+        <v>-136</v>
       </c>
       <c r="E16">
-        <v>-146</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
         <v>71</v>
       </c>
       <c r="G16">
-        <v>824400</v>
+        <v>824884</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2241,46 +2196,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>0.2529</v>
+        <v>0.193</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="P16">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="Q16">
-        <v>0.2935</v>
+        <v>0.1622</v>
       </c>
       <c r="R16">
-        <v>0.315</v>
+        <v>0.357</v>
       </c>
       <c r="S16" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.1514</v>
+        <v>0.1789</v>
       </c>
       <c r="U16">
-        <v>0.1692</v>
+        <v>0.1783</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2154</v>
+        <v>0.1991</v>
       </c>
       <c r="X16">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y16">
-        <v>0.9934</v>
+        <v>0.88</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2289,22 +2244,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.71</v>
+        <v>2.74</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF16">
-        <v>0.2657</v>
+        <v>0.182</v>
       </c>
       <c r="AG16">
-        <v>0.6739</v>
+        <v>0.8008</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>3.71</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2312,28 +2267,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D17">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="E17">
         <v>-104</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17">
-        <v>824157</v>
+        <v>823914</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2345,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2265</v>
+        <v>0.4056</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -2354,34 +2309,34 @@
         <v>106</v>
       </c>
       <c r="P17">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="Q17">
-        <v>0.1792</v>
+        <v>0.4528</v>
       </c>
       <c r="R17">
         <v>0.346</v>
       </c>
       <c r="S17" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2068</v>
+        <v>0.2164</v>
       </c>
       <c r="U17">
-        <v>0.1978</v>
+        <v>0.2159</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2154</v>
+        <v>0.2072</v>
       </c>
       <c r="X17">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y17">
-        <v>0.9979</v>
+        <v>0.9577</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2390,22 +2345,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.3</v>
+        <v>8.95</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2102</v>
+        <v>0.4219</v>
       </c>
       <c r="AG17">
-        <v>0.9205</v>
+        <v>0.9687</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM17">
-        <v>4.3</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2413,28 +2368,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>4.5</v>
       </c>
       <c r="D18">
-        <v>126</v>
+        <v>-160</v>
       </c>
       <c r="E18">
-        <v>-150</v>
+        <v>134</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18">
-        <v>824157</v>
+        <v>823914</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2446,43 +2401,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.16</v>
+        <v>0.1911</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="P18">
-        <v>4.02</v>
+        <v>4.09</v>
       </c>
       <c r="Q18">
-        <v>0.16</v>
+        <v>0.2479</v>
       </c>
       <c r="R18">
-        <v>0.273</v>
+        <v>0.377</v>
       </c>
       <c r="S18" t="s">
         <v>69</v>
       </c>
       <c r="T18">
-        <v>0.2013</v>
+        <v>0.2056</v>
       </c>
       <c r="U18">
-        <v>0.1913</v>
+        <v>0.2348</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2251</v>
+        <v>0.2192</v>
       </c>
       <c r="X18">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y18">
-        <v>0.9945</v>
+        <v>0.9938</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2491,22 +2446,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.56</v>
+        <v>4.87</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF18">
-        <v>0.16</v>
+        <v>0.2125</v>
       </c>
       <c r="AG18">
-        <v>0.896</v>
+        <v>0.9204</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.56</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2514,67 +2469,76 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="C19">
+        <v>5.5</v>
+      </c>
+      <c r="D19">
+        <v>107</v>
+      </c>
+      <c r="E19">
+        <v>-113</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19">
-        <v>823671</v>
+        <v>823347</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
+        <v>5.7</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>6</v>
       </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
       <c r="M19">
-        <v>0.2968</v>
+        <v>0.2157</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P19">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="Q19">
-        <v>0.3077</v>
+        <v>0.1953</v>
       </c>
       <c r="R19">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2046</v>
+        <v>0.2353</v>
       </c>
       <c r="U19">
-        <v>0.1916</v>
+        <v>0.2672</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2226</v>
+        <v>0.2352</v>
       </c>
       <c r="X19">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y19">
-        <v>0.9625</v>
+        <v>1.0844</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2583,22 +2547,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.52</v>
+        <v>5.5</v>
       </c>
       <c r="AE19" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="AF19">
-        <v>0.3011</v>
+        <v>0.2077</v>
       </c>
       <c r="AG19">
-        <v>0.9108</v>
+        <v>1.0535</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>6.52</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2606,28 +2570,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20">
+        <v>4.5</v>
+      </c>
+      <c r="D20">
+        <v>-132</v>
+      </c>
+      <c r="E20">
+        <v>106</v>
+      </c>
+      <c r="F20" t="s">
         <v>77</v>
       </c>
-      <c r="C20">
-        <v>5.5</v>
-      </c>
-      <c r="D20">
-        <v>127</v>
-      </c>
-      <c r="E20">
-        <v>-140</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
       <c r="G20">
-        <v>823671</v>
+        <v>823347</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2639,43 +2603,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2472</v>
+        <v>0.261</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P20">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="Q20">
-        <v>0.3028</v>
+        <v>0.2476</v>
       </c>
       <c r="R20">
-        <v>0.353</v>
+        <v>0.344</v>
       </c>
       <c r="S20" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.183</v>
+        <v>0.1892</v>
       </c>
       <c r="U20">
-        <v>0.1849</v>
+        <v>0.1837</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2364</v>
+        <v>0.2167</v>
       </c>
       <c r="X20">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y20">
-        <v>0.9607</v>
+        <v>0.9661</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2684,22 +2648,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.65</v>
+        <v>4.02</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF20">
-        <v>0.2668</v>
+        <v>0.2564</v>
       </c>
       <c r="AG20">
-        <v>0.8147</v>
+        <v>0.847</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.65</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2707,28 +2671,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D21">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E21">
-        <v>-123</v>
+        <v>-132</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21">
-        <v>823347</v>
+        <v>823990</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2740,43 +2704,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2157</v>
+        <v>0.2816</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="P21">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="Q21">
-        <v>0.1953</v>
+        <v>0.3235</v>
       </c>
       <c r="R21">
-        <v>0.39</v>
+        <v>0.338</v>
       </c>
       <c r="S21" t="s">
         <v>69</v>
       </c>
       <c r="T21">
-        <v>0.2155</v>
+        <v>0.201</v>
       </c>
       <c r="U21">
-        <v>0.2394</v>
+        <v>0.2039</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2352</v>
+        <v>0.2145</v>
       </c>
       <c r="X21">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y21">
-        <v>1.0279</v>
+        <v>0.9609</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2785,22 +2749,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.75</v>
+        <v>5.9</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF21">
-        <v>0.2077</v>
+        <v>0.2958</v>
       </c>
       <c r="AG21">
-        <v>0.9595</v>
+        <v>0.8998</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.75</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2808,28 +2772,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22">
+        <v>3.5</v>
+      </c>
+      <c r="D22">
+        <v>132</v>
+      </c>
+      <c r="E22">
+        <v>-150</v>
+      </c>
+      <c r="F22" t="s">
         <v>80</v>
       </c>
-      <c r="C22">
-        <v>4.5</v>
-      </c>
-      <c r="D22">
-        <v>-120</v>
-      </c>
-      <c r="E22">
-        <v>113</v>
-      </c>
-      <c r="F22" t="s">
-        <v>79</v>
-      </c>
       <c r="G22">
-        <v>823347</v>
+        <v>823990</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2841,43 +2805,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.261</v>
+        <v>0.1242</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="P22">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="Q22">
-        <v>0.2476</v>
+        <v>0.1339</v>
       </c>
       <c r="R22">
-        <v>0.344</v>
+        <v>0.359</v>
       </c>
       <c r="S22" t="s">
         <v>69</v>
       </c>
       <c r="T22">
-        <v>0.1992</v>
+        <v>0.2683</v>
       </c>
       <c r="U22">
-        <v>0.1889</v>
+        <v>0.2598</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2167</v>
+        <v>0.2507</v>
       </c>
       <c r="X22">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y22">
-        <v>0.9737</v>
+        <v>1.0431</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2886,22 +2850,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.24</v>
+        <v>3.58</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF22">
-        <v>0.2564</v>
+        <v>0.1277</v>
       </c>
       <c r="AG22">
-        <v>0.8866</v>
+        <v>1.201</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.24</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2909,28 +2873,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D23">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E23">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23">
-        <v>824884</v>
+        <v>824966</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2942,43 +2906,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1712</v>
+        <v>0.2614</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P23">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="Q23">
-        <v>0.1719</v>
+        <v>0.2787</v>
       </c>
       <c r="R23">
-        <v>0.39</v>
+        <v>0.379</v>
       </c>
       <c r="S23" t="s">
         <v>69</v>
       </c>
       <c r="T23">
-        <v>0.2321</v>
+        <v>0.2569</v>
       </c>
       <c r="U23">
-        <v>0.2244</v>
+        <v>0.2251</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2086</v>
+        <v>0.2494</v>
       </c>
       <c r="X23">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y23">
-        <v>0.9944</v>
+        <v>1.0317</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2987,22 +2951,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.33</v>
+        <v>7.25</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.1715</v>
+        <v>0.268</v>
       </c>
       <c r="AG23">
-        <v>1.0331</v>
+        <v>1.1501</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM23">
-        <v>4.33</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3010,76 +2974,34 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24">
+        <v>4.5</v>
+      </c>
+      <c r="D24">
+        <v>-102</v>
+      </c>
+      <c r="E24">
+        <v>-103</v>
+      </c>
+      <c r="F24" t="s">
         <v>83</v>
       </c>
-      <c r="C24">
-        <v>3.5</v>
-      </c>
-      <c r="D24">
-        <v>-137</v>
-      </c>
-      <c r="E24">
-        <v>115</v>
-      </c>
-      <c r="F24" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24">
-        <v>824884</v>
+      <c r="G24" t="s">
+        <v>44</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24">
-        <v>5</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
-      <c r="M24">
-        <v>0.193</v>
-      </c>
-      <c r="N24">
-        <v>5</v>
-      </c>
-      <c r="O24">
-        <v>111</v>
-      </c>
-      <c r="P24">
-        <v>4.27</v>
-      </c>
-      <c r="Q24">
-        <v>0.1622</v>
-      </c>
-      <c r="R24">
-        <v>0.357</v>
-      </c>
       <c r="S24" t="s">
-        <v>43</v>
-      </c>
-      <c r="T24">
-        <v>0.1789</v>
-      </c>
-      <c r="U24">
-        <v>0.1783</v>
-      </c>
-      <c r="V24">
-        <v>9</v>
-      </c>
-      <c r="W24">
-        <v>0.1991</v>
-      </c>
-      <c r="X24">
-        <v>0.2246</v>
-      </c>
-      <c r="Y24">
-        <v>0.88</v>
+        <v>44</v>
+      </c>
+      <c r="V24" t="s">
+        <v>44</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3087,23 +3009,8 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
-      <c r="AD24">
-        <v>2.72</v>
-      </c>
       <c r="AE24" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF24">
-        <v>0.182</v>
-      </c>
-      <c r="AG24">
-        <v>0.7963</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>2.72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3111,28 +3018,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-118</v>
+        <v>115</v>
       </c>
       <c r="E25">
-        <v>-103</v>
+        <v>-129</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G25">
-        <v>823914</v>
+        <v>824239</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3144,43 +3051,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.4056</v>
+        <v>0.1811</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="P25">
-        <v>3.78</v>
+        <v>4.46</v>
       </c>
       <c r="Q25">
-        <v>0.4528</v>
+        <v>0.1849</v>
       </c>
       <c r="R25">
-        <v>0.346</v>
+        <v>0.373</v>
       </c>
       <c r="S25" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2838</v>
+        <v>0.1831</v>
       </c>
       <c r="U25">
-        <v>0.2206</v>
+        <v>0.2045</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2072</v>
+        <v>0.2272</v>
       </c>
       <c r="X25">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y25">
-        <v>1.0014</v>
+        <v>0.9736</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3189,22 +3096,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>12.2</v>
+        <v>3.23</v>
       </c>
       <c r="AE25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AF25">
-        <v>0.4219</v>
+        <v>0.1825</v>
       </c>
       <c r="AG25">
-        <v>1.2632</v>
+        <v>0.8198</v>
       </c>
       <c r="AH25">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>11.43</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3212,28 +3119,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26">
         <v>5.5</v>
       </c>
       <c r="D26">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E26">
-        <v>-150</v>
+        <v>-128</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G26">
-        <v>823914</v>
+        <v>824239</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3245,43 +3152,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1911</v>
+        <v>0.2219</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="P26">
-        <v>4.09</v>
+        <v>3.9</v>
       </c>
       <c r="Q26">
-        <v>0.2479</v>
+        <v>0.1966</v>
       </c>
       <c r="R26">
-        <v>0.377</v>
+        <v>0.369</v>
       </c>
       <c r="S26" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2056</v>
+        <v>0.2392</v>
       </c>
       <c r="U26">
-        <v>0.2348</v>
+        <v>0.2457</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2192</v>
+        <v>0.2366</v>
       </c>
       <c r="X26">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y26">
-        <v>0.9938</v>
+        <v>1.0768</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3290,22 +3197,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.84</v>
+        <v>5.76</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF26">
         <v>0.2125</v>
       </c>
       <c r="AG26">
-        <v>0.9152</v>
+        <v>1.0711</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.84</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3313,28 +3220,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <v>3.5</v>
       </c>
       <c r="D27">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E27">
-        <v>-150</v>
+        <v>-125</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27">
-        <v>823990</v>
+        <v>824644</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3346,43 +3253,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1242</v>
+        <v>0.1691</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P27">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="Q27">
-        <v>0.1339</v>
+        <v>0.1802</v>
       </c>
       <c r="R27">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="S27" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2683</v>
+        <v>0.2474</v>
       </c>
       <c r="U27">
-        <v>0.2598</v>
+        <v>0.2364</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2507</v>
+        <v>0.2174</v>
       </c>
       <c r="X27">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y27">
-        <v>1.0431</v>
+        <v>0.9668</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3391,22 +3298,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.56</v>
+        <v>4.16</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF27">
-        <v>0.1277</v>
+        <v>0.1731</v>
       </c>
       <c r="AG27">
-        <v>1.1943</v>
+        <v>1.1077</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.56</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3414,28 +3321,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28">
+        <v>4.5</v>
+      </c>
+      <c r="D28">
+        <v>-106</v>
+      </c>
+      <c r="E28">
+        <v>-106</v>
+      </c>
+      <c r="F28" t="s">
         <v>89</v>
       </c>
-      <c r="C28">
-        <v>6.5</v>
-      </c>
-      <c r="D28">
-        <v>115</v>
-      </c>
-      <c r="E28">
-        <v>-137</v>
-      </c>
-      <c r="F28" t="s">
-        <v>88</v>
-      </c>
       <c r="G28">
-        <v>823990</v>
+        <v>824644</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3447,43 +3354,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2816</v>
+        <v>0.1921</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="P28">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="Q28">
-        <v>0.3235</v>
+        <v>0.1241</v>
       </c>
       <c r="R28">
-        <v>0.338</v>
+        <v>0.407</v>
       </c>
       <c r="S28" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.201</v>
+        <v>0.2533</v>
       </c>
       <c r="U28">
-        <v>0.2039</v>
+        <v>0.2142</v>
       </c>
       <c r="V28">
         <v>8</v>
       </c>
       <c r="W28">
-        <v>0.2145</v>
+        <v>0.1835</v>
       </c>
       <c r="X28">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y28">
-        <v>0.9609</v>
+        <v>0.9265</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3492,22 +3399,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.87</v>
+        <v>4.08</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF28">
-        <v>0.2958</v>
+        <v>0.1644</v>
       </c>
       <c r="AG28">
-        <v>0.8947</v>
+        <v>1.1341</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.87</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3515,76 +3422,67 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29">
-        <v>6.5</v>
-      </c>
-      <c r="D29">
-        <v>128</v>
-      </c>
-      <c r="E29">
-        <v>-148</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="G29">
-        <v>824966</v>
+        <v>822775</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I29">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>0.2614</v>
+        <v>0.2262</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="P29">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="Q29">
-        <v>0.2787</v>
+        <v>0.1667</v>
       </c>
       <c r="R29">
-        <v>0.379</v>
+        <v>0.107</v>
       </c>
       <c r="S29" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2569</v>
+        <v>0.2544</v>
       </c>
       <c r="U29">
-        <v>0.2251</v>
+        <v>0.2579</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2494</v>
+        <v>0.2434</v>
       </c>
       <c r="X29">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y29">
-        <v>1.0317</v>
+        <v>1.0475</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3593,22 +3491,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>7.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AF29">
-        <v>0.268</v>
+        <v>0.2198</v>
       </c>
       <c r="AG29">
-        <v>1.1437</v>
+        <v>1.1389</v>
       </c>
       <c r="AH29">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>6.44</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3618,17 +3516,26 @@
       <c r="B30" t="s">
         <v>92</v>
       </c>
+      <c r="C30">
+        <v>3.5</v>
+      </c>
+      <c r="D30">
+        <v>120</v>
+      </c>
+      <c r="E30">
+        <v>-140</v>
+      </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="G30">
-        <v>824966</v>
+        <v>823184</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I30">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3637,46 +3544,46 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>0.2106</v>
+        <v>0.1481</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="P30">
-        <v>4.19</v>
+        <v>4.8</v>
       </c>
       <c r="Q30">
-        <v>0.2174</v>
+        <v>0.0964</v>
       </c>
       <c r="R30">
-        <v>0.365</v>
+        <v>0.293</v>
       </c>
       <c r="S30" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2141</v>
+        <v>0.243</v>
       </c>
       <c r="U30">
-        <v>0.2308</v>
+        <v>0.216</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>0.2207</v>
+        <v>0.2021</v>
       </c>
       <c r="X30">
-        <v>0.2246</v>
+        <v>0.2234</v>
       </c>
       <c r="Y30">
-        <v>1.0405</v>
+        <v>0.9007</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3685,22 +3592,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>4.82</v>
+        <v>2.79</v>
       </c>
       <c r="AE30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF30">
-        <v>0.2131</v>
+        <v>0.1329</v>
       </c>
       <c r="AG30">
-        <v>0.9529</v>
+        <v>1.0877</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>4.82</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3710,32 +3617,65 @@
       <c r="B31" t="s">
         <v>93</v>
       </c>
-      <c r="C31">
-        <v>6.5</v>
-      </c>
-      <c r="D31">
-        <v>-103</v>
-      </c>
-      <c r="E31">
-        <v>-120</v>
-      </c>
       <c r="F31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
+        <v>62</v>
+      </c>
+      <c r="G31">
+        <v>824400</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.1484</v>
+      </c>
+      <c r="N31">
+        <v>4</v>
+      </c>
+      <c r="O31">
+        <v>14</v>
+      </c>
+      <c r="P31">
+        <v>4.2</v>
+      </c>
+      <c r="Q31">
+        <v>0.2143</v>
+      </c>
+      <c r="R31">
+        <v>0.065</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.1578</v>
+      </c>
+      <c r="U31">
+        <v>0.1696</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.2251</v>
+      </c>
+      <c r="X31">
+        <v>0.2234</v>
+      </c>
+      <c r="Y31">
+        <v>0.88</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3743,8 +3683,23 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
+      <c r="AD31">
+        <v>0.4</v>
+      </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AF31">
+        <v>0.1527</v>
+      </c>
+      <c r="AG31">
+        <v>0.7065</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3754,32 +3709,65 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="C32">
-        <v>4.5</v>
-      </c>
-      <c r="D32">
-        <v>-105</v>
-      </c>
-      <c r="E32">
-        <v>-115</v>
-      </c>
       <c r="F32" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" t="s">
-        <v>44</v>
+        <v>67</v>
+      </c>
+      <c r="G32">
+        <v>823671</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I32">
+        <v>6</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.2968</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32">
+        <v>130</v>
+      </c>
+      <c r="P32">
+        <v>4.13</v>
+      </c>
+      <c r="Q32">
+        <v>0.3077</v>
+      </c>
+      <c r="R32">
+        <v>0.394</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
-      </c>
-      <c r="V32" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T32">
+        <v>0.2046</v>
+      </c>
+      <c r="U32">
+        <v>0.1916</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>0.2226</v>
+      </c>
+      <c r="X32">
+        <v>0.2234</v>
+      </c>
+      <c r="Y32">
+        <v>0.9625</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3787,8 +3775,115 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
+      <c r="AD32">
+        <v>6.56</v>
+      </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="AF32">
+        <v>0.3011</v>
+      </c>
+      <c r="AG32">
+        <v>0.916</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33">
+        <v>824966</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33">
+        <v>5.4</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.2106</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>115</v>
+      </c>
+      <c r="P33">
+        <v>4.19</v>
+      </c>
+      <c r="Q33">
+        <v>0.2174</v>
+      </c>
+      <c r="R33">
+        <v>0.365</v>
+      </c>
+      <c r="S33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T33">
+        <v>0.2141</v>
+      </c>
+      <c r="U33">
+        <v>0.2308</v>
+      </c>
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33">
+        <v>0.2207</v>
+      </c>
+      <c r="X33">
+        <v>0.2234</v>
+      </c>
+      <c r="Y33">
+        <v>1.0405</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD33">
+        <v>4.84</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF33">
+        <v>0.2131</v>
+      </c>
+      <c r="AG33">
+        <v>0.9583</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>4.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-15.xlsx
+++ b/data/k-props/2026-08-15.xlsx
@@ -133,75 +133,102 @@
     <t>08/15/2026</t>
   </si>
   <si>
+    <t>Anthony Kay</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
     <t>Cam Schlittler</t>
   </si>
   <si>
     <t>New York Yankees @ Toronto Blue Jays</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>&gt;=7</t>
   </si>
   <si>
+    <t>Braydon Fisher</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Michael Lorenzen</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
+  </si>
+  <si>
     <t>Logan Webb</t>
   </si>
   <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Brad Lord</t>
   </si>
   <si>
     <t>Washington Nationals @ New York Mets</t>
   </si>
   <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
     <t>Sean Manaea</t>
   </si>
   <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
     <t>Ian Seymour</t>
   </si>
   <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Kyle Bradish</t>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
   </si>
   <si>
     <t>Brady Singer</t>
   </si>
   <si>
-    <t>Miami Marlins @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
+    <t>Wandy Peralta</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Cleveland Guardians</t>
   </si>
   <si>
     <t>Joey Cantillo</t>
   </si>
   <si>
-    <t>San Diego Padres @ Cleveland Guardians</t>
-  </si>
-  <si>
     <t>Emerson Hancock</t>
   </si>
   <si>
@@ -211,94 +238,67 @@
     <t>Hayden Wesneski</t>
   </si>
   <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Justin Wrobleski</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
     <t>Jesus Luzardo</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Justin Wrobleski</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
-  </si>
-  <si>
     <t>JT Ginn</t>
-  </si>
-  <si>
-    <t>Anthony Kay</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Braydon Fisher</t>
-  </si>
-  <si>
-    <t>Michael Lorenzen</t>
-  </si>
-  <si>
-    <t>Wandy Peralta</t>
-  </si>
-  <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
   </si>
 </sst>
 </file>
@@ -812,25 +812,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-140</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>105</v>
+        <v>-129</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>822775</v>
+        <v>824239</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -839,46 +839,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>0.3143</v>
+        <v>0.1811</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="P2">
-        <v>3.96</v>
+        <v>4.46</v>
       </c>
       <c r="Q2">
-        <v>0.3905</v>
+        <v>0.1849</v>
       </c>
       <c r="R2">
-        <v>0.344</v>
+        <v>0.373</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.243</v>
+        <v>0.1831</v>
       </c>
       <c r="U2">
-        <v>0.2233</v>
+        <v>0.2045</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.1893</v>
+        <v>0.2272</v>
       </c>
       <c r="X2">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y2">
-        <v>1.0898</v>
+        <v>0.9736</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -887,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>9.24</v>
+        <v>3.19</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.3405</v>
+        <v>0.1825</v>
       </c>
       <c r="AG2">
-        <v>1.0877</v>
+        <v>0.8097</v>
       </c>
       <c r="AH2">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>8.47</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -916,22 +916,22 @@
         <v>5.5</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>-128</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>823184</v>
+        <v>824239</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -940,46 +940,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1922</v>
+        <v>0.2219</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="P3">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
-        <v>0.1845</v>
+        <v>0.1966</v>
       </c>
       <c r="R3">
-        <v>0.34</v>
+        <v>0.369</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2245</v>
+        <v>0.2392</v>
       </c>
       <c r="U3">
-        <v>0.2071</v>
+        <v>0.2457</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2164</v>
+        <v>0.2366</v>
       </c>
       <c r="X3">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y3">
-        <v>0.9947</v>
+        <v>1.0768</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -988,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.66</v>
+        <v>5.69</v>
       </c>
       <c r="AE3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1896</v>
+        <v>0.2125</v>
       </c>
       <c r="AG3">
-        <v>1.0049</v>
+        <v>1.0578</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.66</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1011,76 +1011,76 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E4">
-        <v>-164</v>
+        <v>-125</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>823588</v>
+        <v>824644</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I4">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2121</v>
+        <v>0.1691</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="P4">
-        <v>4.28</v>
+        <v>4.08</v>
       </c>
       <c r="Q4">
-        <v>0.2174</v>
+        <v>0.1802</v>
       </c>
       <c r="R4">
-        <v>0.103</v>
+        <v>0.357</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2573</v>
+        <v>0.2474</v>
       </c>
       <c r="U4">
-        <v>0.2469</v>
+        <v>0.2364</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2248</v>
+        <v>0.2172</v>
       </c>
       <c r="X4">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y4">
-        <v>0.9929</v>
+        <v>0.9668</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1089,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>1.74</v>
+        <v>4.1</v>
       </c>
       <c r="AE4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2127</v>
+        <v>0.1731</v>
       </c>
       <c r="AG4">
-        <v>1.1518</v>
+        <v>1.094</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.74</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1112,28 +1112,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-150</v>
+        <v>-106</v>
       </c>
       <c r="E5">
-        <v>122</v>
+        <v>-106</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>823588</v>
+        <v>824644</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1145,43 +1145,43 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2363</v>
+        <v>0.1921</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="P5">
-        <v>4.32</v>
+        <v>4.16</v>
       </c>
       <c r="Q5">
-        <v>0.2596</v>
+        <v>0.1241</v>
       </c>
       <c r="R5">
-        <v>0.342</v>
+        <v>0.407</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2143</v>
+        <v>0.2533</v>
       </c>
       <c r="U5">
-        <v>0.2183</v>
+        <v>0.2142</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>0.2345</v>
+        <v>0.1812</v>
       </c>
       <c r="X5">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y5">
-        <v>1.0233</v>
+        <v>0.9265</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1190,22 +1190,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.42</v>
+        <v>4.03</v>
       </c>
       <c r="AE5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2443</v>
+        <v>0.1644</v>
       </c>
       <c r="AG5">
-        <v>0.9595</v>
+        <v>1.1201</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.42</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1213,28 +1213,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>6.5</v>
       </c>
       <c r="D6">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="E6">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>822941</v>
+        <v>822775</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1243,46 +1243,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>0.2842</v>
+        <v>0.314</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="P6">
-        <v>4.13</v>
+        <v>3.96</v>
       </c>
       <c r="Q6">
-        <v>0.3398</v>
+        <v>0.3894</v>
       </c>
       <c r="R6">
-        <v>0.34</v>
+        <v>0.361</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2644</v>
+        <v>0.243</v>
       </c>
       <c r="U6">
-        <v>0.2523</v>
+        <v>0.2233</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2573</v>
+        <v>0.1893</v>
       </c>
       <c r="X6">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y6">
-        <v>1.0233</v>
+        <v>1.0898</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1291,22 +1291,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.85</v>
+        <v>9.25</v>
       </c>
       <c r="AE6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AF6">
-        <v>0.3031</v>
+        <v>0.3412</v>
       </c>
       <c r="AG6">
-        <v>1.1838</v>
+        <v>1.0743</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM6">
-        <v>6.85</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1314,37 +1314,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7">
-        <v>4.5</v>
-      </c>
-      <c r="D7">
-        <v>-104</v>
-      </c>
-      <c r="E7">
-        <v>-115</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7">
+        <v>822775</v>
+      </c>
+      <c r="H7" t="s">
         <v>54</v>
       </c>
-      <c r="G7">
-        <v>822941</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
       <c r="I7">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0.2262</v>
@@ -1353,37 +1344,37 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="P7">
-        <v>4.21</v>
+        <v>4.06</v>
       </c>
       <c r="Q7">
-        <v>0.1887</v>
+        <v>0.1667</v>
       </c>
       <c r="R7">
-        <v>0.346</v>
+        <v>0.107</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.1815</v>
+        <v>0.2544</v>
       </c>
       <c r="U7">
-        <v>0.1767</v>
+        <v>0.2579</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.1896</v>
+        <v>0.2434</v>
       </c>
       <c r="X7">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y7">
-        <v>0.88</v>
+        <v>1.0475</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1392,22 +1383,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.55</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2132</v>
+        <v>0.2198</v>
       </c>
       <c r="AG7">
-        <v>0.8127</v>
+        <v>1.1249</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.55</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1415,28 +1406,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E8">
-        <v>-135</v>
+        <v>-140</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>824480</v>
+        <v>823184</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1448,43 +1439,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1887</v>
+        <v>0.1459</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="P8">
-        <v>4.43</v>
+        <v>4.8</v>
       </c>
       <c r="Q8">
-        <v>0.1875</v>
+        <v>0.0909</v>
       </c>
       <c r="R8">
-        <v>0.39</v>
+        <v>0.331</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2698</v>
+        <v>0.243</v>
       </c>
       <c r="U8">
-        <v>0.2556</v>
+        <v>0.216</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2115</v>
+        <v>0.2021</v>
       </c>
       <c r="X8">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y8">
-        <v>0.9392</v>
+        <v>0.9007</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1493,22 +1484,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.92</v>
+        <v>2.72</v>
       </c>
       <c r="AE8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1882</v>
+        <v>0.1277</v>
       </c>
       <c r="AG8">
-        <v>1.2079</v>
+        <v>1.0743</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.92</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1516,28 +1507,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>-115</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>824480</v>
+        <v>823184</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1546,46 +1537,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>0.1991</v>
+        <v>0.1978</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="P9">
-        <v>4.41</v>
+        <v>4.04</v>
       </c>
       <c r="Q9">
-        <v>0.1915</v>
+        <v>0.2119</v>
       </c>
       <c r="R9">
-        <v>0.32</v>
+        <v>0.371</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2706</v>
+        <v>0.2245</v>
       </c>
       <c r="U9">
-        <v>0.2672</v>
+        <v>0.2071</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2532</v>
+        <v>0.2164</v>
       </c>
       <c r="X9">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y9">
-        <v>1.076</v>
+        <v>0.9947</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1594,22 +1585,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.48</v>
+        <v>5.07</v>
       </c>
       <c r="AE9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1966</v>
+        <v>0.203</v>
       </c>
       <c r="AG9">
-        <v>1.2113</v>
+        <v>0.9924</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.48</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1617,76 +1608,76 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D10">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E10">
-        <v>-138</v>
+        <v>-164</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>824400</v>
+        <v>823588</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I10">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>0.2529</v>
+        <v>0.2119</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="P10">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="Q10">
-        <v>0.2935</v>
+        <v>0.2069</v>
       </c>
       <c r="R10">
-        <v>0.315</v>
+        <v>0.127</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.174</v>
+        <v>0.2573</v>
       </c>
       <c r="U10">
-        <v>0.1783</v>
+        <v>0.2469</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2154</v>
+        <v>0.2248</v>
       </c>
       <c r="X10">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y10">
-        <v>1.0658</v>
+        <v>0.9929</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1695,22 +1686,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.61</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2657</v>
+        <v>0.2113</v>
       </c>
       <c r="AG10">
-        <v>0.7791</v>
+        <v>1.1376</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.61</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1718,22 +1709,22 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>-150</v>
       </c>
       <c r="E11">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G11">
-        <v>824157</v>
+        <v>823588</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
@@ -1751,43 +1742,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2265</v>
+        <v>0.2399</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="P11">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="Q11">
-        <v>0.1792</v>
+        <v>0.2672</v>
       </c>
       <c r="R11">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2108</v>
+        <v>0.2143</v>
       </c>
       <c r="U11">
-        <v>0.2017</v>
+        <v>0.2183</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2154</v>
+        <v>0.2345</v>
       </c>
       <c r="X11">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y11">
-        <v>0.9861</v>
+        <v>1.0233</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1796,22 +1787,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>4.36</v>
+        <v>5.73</v>
       </c>
       <c r="AE11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2102</v>
+        <v>0.2499</v>
       </c>
       <c r="AG11">
-        <v>0.9437</v>
+        <v>0.9476</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>4.36</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1819,28 +1810,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>124</v>
+        <v>-104</v>
       </c>
       <c r="E12">
-        <v>-135</v>
+        <v>-115</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>824157</v>
+        <v>822941</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1852,43 +1843,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.16</v>
+        <v>0.2262</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="P12">
-        <v>4.02</v>
+        <v>4.21</v>
       </c>
       <c r="Q12">
-        <v>0.16</v>
+        <v>0.1887</v>
       </c>
       <c r="R12">
-        <v>0.273</v>
+        <v>0.346</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2032</v>
+        <v>0.1815</v>
       </c>
       <c r="U12">
-        <v>0.186</v>
+        <v>0.1767</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2251</v>
+        <v>0.1896</v>
       </c>
       <c r="X12">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y12">
-        <v>0.9867</v>
+        <v>0.88</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1897,22 +1888,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.16</v>
+        <v>0.2132</v>
       </c>
       <c r="AG12">
-        <v>0.9099</v>
+        <v>0.8026</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1920,34 +1911,76 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>6.5</v>
       </c>
       <c r="D13">
-        <v>102</v>
+        <v>-120</v>
       </c>
       <c r="E13">
-        <v>-120</v>
+        <v>118</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" t="s">
-        <v>44</v>
+        <v>62</v>
+      </c>
+      <c r="G13">
+        <v>822941</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I13">
+        <v>4.5</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
+      <c r="M13">
+        <v>0.2842</v>
+      </c>
+      <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13">
+        <v>103</v>
+      </c>
+      <c r="P13">
+        <v>4.13</v>
+      </c>
+      <c r="Q13">
+        <v>0.3398</v>
+      </c>
+      <c r="R13">
+        <v>0.34</v>
+      </c>
       <c r="S13" t="s">
-        <v>44</v>
-      </c>
-      <c r="V13" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T13">
+        <v>0.2644</v>
+      </c>
+      <c r="U13">
+        <v>0.2523</v>
+      </c>
+      <c r="V13">
+        <v>9</v>
+      </c>
+      <c r="W13">
+        <v>0.2573</v>
+      </c>
+      <c r="X13">
+        <v>0.2262</v>
+      </c>
+      <c r="Y13">
+        <v>1.0233</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1955,8 +1988,23 @@
       <c r="AC13" t="s">
         <v>44</v>
       </c>
+      <c r="AD13">
+        <v>6.77</v>
+      </c>
       <c r="AE13" t="s">
-        <v>44</v>
+        <v>64</v>
+      </c>
+      <c r="AF13">
+        <v>0.3031</v>
+      </c>
+      <c r="AG13">
+        <v>1.1692</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>6.77</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1964,28 +2012,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D14">
-        <v>118</v>
+        <v>-103</v>
       </c>
       <c r="E14">
-        <v>-140</v>
+        <v>-115</v>
       </c>
       <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>824480</v>
+      </c>
+      <c r="H14" t="s">
         <v>67</v>
       </c>
-      <c r="G14">
-        <v>823671</v>
-      </c>
-      <c r="H14" t="s">
-        <v>42</v>
-      </c>
       <c r="I14">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1997,43 +2045,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2472</v>
+        <v>0.1991</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="P14">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="Q14">
-        <v>0.3028</v>
+        <v>0.1915</v>
       </c>
       <c r="R14">
-        <v>0.353</v>
+        <v>0.32</v>
       </c>
       <c r="S14" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.183</v>
+        <v>0.2706</v>
       </c>
       <c r="U14">
-        <v>0.1849</v>
+        <v>0.2672</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2364</v>
+        <v>0.2532</v>
       </c>
       <c r="X14">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y14">
-        <v>0.9607</v>
+        <v>1.076</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2042,22 +2090,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="AE14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2668</v>
+        <v>0.1966</v>
       </c>
       <c r="AG14">
-        <v>0.8193</v>
+        <v>1.1964</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2065,28 +2113,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E15">
-        <v>-149</v>
+        <v>-135</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G15">
-        <v>824884</v>
+        <v>824480</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2098,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1712</v>
+        <v>0.1887</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -2107,10 +2155,10 @@
         <v>128</v>
       </c>
       <c r="P15">
-        <v>4.12</v>
+        <v>4.43</v>
       </c>
       <c r="Q15">
-        <v>0.1719</v>
+        <v>0.1875</v>
       </c>
       <c r="R15">
         <v>0.39</v>
@@ -2119,22 +2167,22 @@
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2562</v>
+        <v>0.2698</v>
       </c>
       <c r="U15">
-        <v>0.2259</v>
+        <v>0.2556</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2086</v>
+        <v>0.2115</v>
       </c>
       <c r="X15">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y15">
-        <v>0.9928</v>
+        <v>0.9392</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2143,22 +2191,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="AE15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1715</v>
+        <v>0.1882</v>
       </c>
       <c r="AG15">
-        <v>1.1471</v>
+        <v>1.193</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2166,73 +2214,64 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16">
-        <v>3.5</v>
-      </c>
-      <c r="D16">
-        <v>-136</v>
-      </c>
-      <c r="E16">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16">
-        <v>824884</v>
+        <v>824400</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>0.193</v>
+        <v>0.1484</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="P16">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="Q16">
-        <v>0.1622</v>
+        <v>0.2143</v>
       </c>
       <c r="R16">
-        <v>0.357</v>
+        <v>0.065</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.1789</v>
+        <v>0.1578</v>
       </c>
       <c r="U16">
-        <v>0.1783</v>
+        <v>0.1696</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.1991</v>
+        <v>0.2251</v>
       </c>
       <c r="X16">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y16">
         <v>0.88</v>
@@ -2244,22 +2283,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>2.74</v>
+        <v>0.39</v>
       </c>
       <c r="AE16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.182</v>
+        <v>0.1527</v>
       </c>
       <c r="AG16">
-        <v>0.8008</v>
+        <v>0.6977</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>2.74</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2267,28 +2306,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="D17">
-        <v>-120</v>
+        <v>113</v>
       </c>
       <c r="E17">
-        <v>-104</v>
+        <v>-138</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>823914</v>
+        <v>824400</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2297,46 +2336,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>0.4056</v>
+        <v>0.2529</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="P17">
-        <v>3.78</v>
+        <v>4.36</v>
       </c>
       <c r="Q17">
-        <v>0.4528</v>
+        <v>0.2935</v>
       </c>
       <c r="R17">
-        <v>0.346</v>
+        <v>0.315</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2164</v>
+        <v>0.174</v>
       </c>
       <c r="U17">
-        <v>0.2159</v>
+        <v>0.1783</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2072</v>
+        <v>0.2154</v>
       </c>
       <c r="X17">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y17">
-        <v>0.9577</v>
+        <v>1.0658</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2345,22 +2384,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>8.95</v>
+        <v>4.55</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.4219</v>
+        <v>0.2657</v>
       </c>
       <c r="AG17">
-        <v>0.9687</v>
+        <v>0.7694</v>
       </c>
       <c r="AH17">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>8.18</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2368,28 +2407,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-160</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>134</v>
+        <v>-104</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18">
-        <v>823914</v>
+        <v>824157</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2401,43 +2440,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1911</v>
+        <v>0.2265</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="P18">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="Q18">
-        <v>0.2479</v>
+        <v>0.1792</v>
       </c>
       <c r="R18">
-        <v>0.377</v>
+        <v>0.346</v>
       </c>
       <c r="S18" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2056</v>
+        <v>0.2108</v>
       </c>
       <c r="U18">
-        <v>0.2348</v>
+        <v>0.2017</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2192</v>
+        <v>0.2154</v>
       </c>
       <c r="X18">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y18">
-        <v>0.9938</v>
+        <v>0.9861</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2446,22 +2485,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.87</v>
+        <v>4.3</v>
       </c>
       <c r="AE18" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2125</v>
+        <v>0.2102</v>
       </c>
       <c r="AG18">
-        <v>0.9204</v>
+        <v>0.932</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.87</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2469,28 +2508,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>-113</v>
+        <v>-135</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G19">
-        <v>823347</v>
+        <v>824157</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2502,43 +2541,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2157</v>
+        <v>0.16</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="P19">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="Q19">
-        <v>0.1953</v>
+        <v>0.16</v>
       </c>
       <c r="R19">
-        <v>0.39</v>
+        <v>0.273</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2353</v>
+        <v>0.2032</v>
       </c>
       <c r="U19">
-        <v>0.2672</v>
+        <v>0.186</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2352</v>
+        <v>0.2251</v>
       </c>
       <c r="X19">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y19">
-        <v>1.0844</v>
+        <v>0.9867</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2547,22 +2586,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="AE19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2077</v>
+        <v>0.16</v>
       </c>
       <c r="AG19">
-        <v>1.0535</v>
+        <v>0.8986</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2570,28 +2609,19 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20">
-        <v>4.5</v>
-      </c>
-      <c r="D20">
-        <v>-132</v>
-      </c>
-      <c r="E20">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G20">
-        <v>823347</v>
+        <v>823671</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2600,46 +2630,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>0.261</v>
+        <v>0.2968</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="P20">
-        <v>4.22</v>
+        <v>4.13</v>
       </c>
       <c r="Q20">
-        <v>0.2476</v>
+        <v>0.3077</v>
       </c>
       <c r="R20">
-        <v>0.344</v>
+        <v>0.394</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.1892</v>
+        <v>0.2046</v>
       </c>
       <c r="U20">
-        <v>0.1837</v>
+        <v>0.1916</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2167</v>
+        <v>0.2226</v>
       </c>
       <c r="X20">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y20">
-        <v>0.9661</v>
+        <v>0.9625</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2648,22 +2678,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.02</v>
+        <v>6.48</v>
       </c>
       <c r="AE20" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="AF20">
-        <v>0.2564</v>
+        <v>0.3011</v>
       </c>
       <c r="AG20">
-        <v>0.847</v>
+        <v>0.9047</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.02</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2671,28 +2701,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E21">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G21">
-        <v>823990</v>
+        <v>823671</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2704,43 +2734,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2816</v>
+        <v>0.2472</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="P21">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="Q21">
-        <v>0.3235</v>
+        <v>0.3028</v>
       </c>
       <c r="R21">
-        <v>0.338</v>
+        <v>0.353</v>
       </c>
       <c r="S21" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.201</v>
+        <v>0.2078</v>
       </c>
       <c r="U21">
-        <v>0.2039</v>
+        <v>0.195</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2145</v>
+        <v>0.2364</v>
       </c>
       <c r="X21">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y21">
-        <v>0.9609</v>
+        <v>0.9562</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2749,22 +2779,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.9</v>
+        <v>5.22</v>
       </c>
       <c r="AE21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2958</v>
+        <v>0.2668</v>
       </c>
       <c r="AG21">
-        <v>0.8998</v>
+        <v>0.9189</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.9</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2772,28 +2802,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C22">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E22">
-        <v>-150</v>
+        <v>-113</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G22">
-        <v>823990</v>
+        <v>823347</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2805,43 +2835,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1242</v>
+        <v>0.2157</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="P22">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="Q22">
-        <v>0.1339</v>
+        <v>0.1953</v>
       </c>
       <c r="R22">
-        <v>0.359</v>
+        <v>0.39</v>
       </c>
       <c r="S22" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2683</v>
+        <v>0.2353</v>
       </c>
       <c r="U22">
-        <v>0.2598</v>
+        <v>0.2672</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2507</v>
+        <v>0.2352</v>
       </c>
       <c r="X22">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y22">
-        <v>1.0431</v>
+        <v>1.0844</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2850,22 +2880,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.58</v>
+        <v>5.43</v>
       </c>
       <c r="AE22" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.1277</v>
+        <v>0.2077</v>
       </c>
       <c r="AG22">
-        <v>1.201</v>
+        <v>1.0405</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>3.58</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2873,28 +2903,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C23">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D23">
-        <v>130</v>
+        <v>-132</v>
       </c>
       <c r="E23">
-        <v>-138</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>824966</v>
+        <v>823347</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2906,43 +2936,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2614</v>
+        <v>0.261</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="P23">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="Q23">
-        <v>0.2787</v>
+        <v>0.2476</v>
       </c>
       <c r="R23">
-        <v>0.379</v>
+        <v>0.344</v>
       </c>
       <c r="S23" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2569</v>
+        <v>0.1892</v>
       </c>
       <c r="U23">
-        <v>0.2251</v>
+        <v>0.1837</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2494</v>
+        <v>0.2167</v>
       </c>
       <c r="X23">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y23">
-        <v>1.0317</v>
+        <v>0.9661</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2951,22 +2981,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>7.25</v>
+        <v>3.97</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.268</v>
+        <v>0.2564</v>
       </c>
       <c r="AG23">
-        <v>1.1501</v>
+        <v>0.8365</v>
       </c>
       <c r="AH23">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>6.48</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2974,34 +3004,76 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C24">
         <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-102</v>
+        <v>120</v>
       </c>
       <c r="E24">
-        <v>-103</v>
+        <v>-149</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" t="s">
-        <v>44</v>
+        <v>82</v>
+      </c>
+      <c r="G24">
+        <v>824884</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I24">
+        <v>6</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
+      <c r="M24">
+        <v>0.1712</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>128</v>
+      </c>
+      <c r="P24">
+        <v>4.12</v>
+      </c>
+      <c r="Q24">
+        <v>0.1719</v>
+      </c>
+      <c r="R24">
+        <v>0.39</v>
+      </c>
       <c r="S24" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T24">
+        <v>0.2562</v>
+      </c>
+      <c r="U24">
+        <v>0.2259</v>
+      </c>
+      <c r="V24">
+        <v>9</v>
+      </c>
+      <c r="W24">
+        <v>0.2086</v>
+      </c>
+      <c r="X24">
+        <v>0.2262</v>
+      </c>
+      <c r="Y24">
+        <v>0.9928</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3009,8 +3081,23 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
+      <c r="AD24">
+        <v>4.74</v>
+      </c>
       <c r="AE24" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF24">
+        <v>0.1715</v>
+      </c>
+      <c r="AG24">
+        <v>1.133</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>4.74</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3018,22 +3105,22 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D25">
+        <v>-136</v>
+      </c>
+      <c r="E25">
         <v>115</v>
       </c>
-      <c r="E25">
-        <v>-129</v>
-      </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G25">
-        <v>824239</v>
+        <v>824884</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
@@ -3051,43 +3138,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.1811</v>
+        <v>0.193</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="P25">
-        <v>4.46</v>
+        <v>4.27</v>
       </c>
       <c r="Q25">
-        <v>0.1849</v>
+        <v>0.1622</v>
       </c>
       <c r="R25">
-        <v>0.373</v>
+        <v>0.357</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.1831</v>
+        <v>0.1789</v>
       </c>
       <c r="U25">
-        <v>0.2045</v>
+        <v>0.1783</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2272</v>
+        <v>0.1991</v>
       </c>
       <c r="X25">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y25">
-        <v>0.9736</v>
+        <v>0.88</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3096,22 +3183,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>3.23</v>
+        <v>2.71</v>
       </c>
       <c r="AE25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1825</v>
+        <v>0.182</v>
       </c>
       <c r="AG25">
-        <v>0.8198</v>
+        <v>0.7909</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>3.23</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3119,22 +3206,22 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C26">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="D26">
-        <v>115</v>
+        <v>-120</v>
       </c>
       <c r="E26">
-        <v>-128</v>
+        <v>-104</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G26">
-        <v>824239</v>
+        <v>823914</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
@@ -3152,43 +3239,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2219</v>
+        <v>0.4056</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="P26">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="Q26">
-        <v>0.1966</v>
+        <v>0.4528</v>
       </c>
       <c r="R26">
-        <v>0.369</v>
+        <v>0.346</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2392</v>
+        <v>0.2164</v>
       </c>
       <c r="U26">
-        <v>0.2457</v>
+        <v>0.2159</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2366</v>
+        <v>0.2072</v>
       </c>
       <c r="X26">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y26">
-        <v>1.0768</v>
+        <v>0.9577</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3197,22 +3284,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>5.76</v>
+        <v>8.84</v>
       </c>
       <c r="AE26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AF26">
-        <v>0.2125</v>
+        <v>0.4219</v>
       </c>
       <c r="AG26">
-        <v>1.0711</v>
+        <v>0.9567</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM26">
-        <v>5.76</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3220,28 +3307,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C27">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27">
-        <v>114</v>
+        <v>-160</v>
       </c>
       <c r="E27">
-        <v>-125</v>
+        <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>824644</v>
+        <v>823914</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3253,43 +3340,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1691</v>
+        <v>0.1911</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="P27">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="Q27">
-        <v>0.1802</v>
+        <v>0.2479</v>
       </c>
       <c r="R27">
-        <v>0.357</v>
+        <v>0.377</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2474</v>
+        <v>0.2645</v>
       </c>
       <c r="U27">
-        <v>0.2364</v>
+        <v>0.2301</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2174</v>
+        <v>0.2192</v>
       </c>
       <c r="X27">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y27">
-        <v>0.9668</v>
+        <v>0.9537</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3298,22 +3385,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.16</v>
+        <v>5.93</v>
       </c>
       <c r="AE27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1731</v>
+        <v>0.2125</v>
       </c>
       <c r="AG27">
-        <v>1.1077</v>
+        <v>1.1697</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>4.16</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3321,28 +3408,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C28">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D28">
-        <v>-106</v>
+        <v>132</v>
       </c>
       <c r="E28">
-        <v>-106</v>
+        <v>-150</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G28">
-        <v>824644</v>
+        <v>823990</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3354,43 +3441,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.1921</v>
+        <v>0.1242</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="P28">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="Q28">
-        <v>0.1241</v>
+        <v>0.1339</v>
       </c>
       <c r="R28">
-        <v>0.407</v>
+        <v>0.359</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="T28">
-        <v>0.2533</v>
+        <v>0.2683</v>
       </c>
       <c r="U28">
-        <v>0.2142</v>
+        <v>0.2598</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>0.1835</v>
+        <v>0.2507</v>
       </c>
       <c r="X28">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y28">
-        <v>0.9265</v>
+        <v>1.0431</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3399,22 +3486,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="AE28" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.1644</v>
+        <v>0.1277</v>
       </c>
       <c r="AG28">
-        <v>1.1341</v>
+        <v>1.1862</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3422,67 +3509,76 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <v>6.5</v>
+      </c>
+      <c r="D29">
+        <v>115</v>
+      </c>
+      <c r="E29">
+        <v>-132</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>822775</v>
+        <v>823990</v>
       </c>
       <c r="H29" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I29">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>0.2262</v>
+        <v>0.2816</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="P29">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="Q29">
-        <v>0.1667</v>
+        <v>0.3235</v>
       </c>
       <c r="R29">
-        <v>0.107</v>
+        <v>0.338</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="T29">
-        <v>0.2544</v>
+        <v>0.201</v>
       </c>
       <c r="U29">
-        <v>0.2579</v>
+        <v>0.2039</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>0.2434</v>
+        <v>0.2145</v>
       </c>
       <c r="X29">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y29">
-        <v>1.0475</v>
+        <v>0.9609</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3491,22 +3587,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>5.83</v>
       </c>
       <c r="AE29" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF29">
-        <v>0.2198</v>
+        <v>0.2958</v>
       </c>
       <c r="AG29">
-        <v>1.1389</v>
+        <v>0.8887</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.2</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3514,28 +3610,28 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30">
+        <v>6.5</v>
+      </c>
+      <c r="D30">
+        <v>130</v>
+      </c>
+      <c r="E30">
+        <v>-138</v>
+      </c>
+      <c r="F30" t="s">
         <v>92</v>
       </c>
-      <c r="C30">
-        <v>3.5</v>
-      </c>
-      <c r="D30">
-        <v>120</v>
-      </c>
-      <c r="E30">
-        <v>-140</v>
-      </c>
-      <c r="F30" t="s">
-        <v>47</v>
-      </c>
       <c r="G30">
-        <v>823184</v>
+        <v>824966</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I30">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3547,43 +3643,43 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>0.1481</v>
+        <v>0.2614</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="P30">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q30">
-        <v>0.0964</v>
+        <v>0.2787</v>
       </c>
       <c r="R30">
-        <v>0.293</v>
+        <v>0.379</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="T30">
-        <v>0.243</v>
+        <v>0.2569</v>
       </c>
       <c r="U30">
-        <v>0.216</v>
+        <v>0.2251</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2021</v>
+        <v>0.2494</v>
       </c>
       <c r="X30">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y30">
-        <v>0.9007</v>
+        <v>1.0317</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3592,22 +3688,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>2.79</v>
+        <v>7.16</v>
       </c>
       <c r="AE30" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AF30">
-        <v>0.1329</v>
+        <v>0.268</v>
       </c>
       <c r="AG30">
-        <v>1.0877</v>
+        <v>1.1359</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="AM30">
-        <v>2.79</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3618,19 +3714,19 @@
         <v>93</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="G31">
-        <v>824400</v>
+        <v>824966</v>
       </c>
       <c r="H31" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -3639,43 +3735,43 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0.1484</v>
+        <v>0.2106</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="Q31">
-        <v>0.2143</v>
+        <v>0.2174</v>
       </c>
       <c r="R31">
-        <v>0.065</v>
+        <v>0.365</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="T31">
-        <v>0.1578</v>
+        <v>0.2141</v>
       </c>
       <c r="U31">
-        <v>0.1696</v>
+        <v>0.2308</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
-        <v>0.2251</v>
+        <v>0.2207</v>
       </c>
       <c r="X31">
-        <v>0.2234</v>
+        <v>0.2262</v>
       </c>
       <c r="Y31">
-        <v>0.88</v>
+        <v>1.0405</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3684,22 +3780,22 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>0.4</v>
+        <v>4.78</v>
       </c>
       <c r="AE31" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF31">
-        <v>0.1527</v>
+        <v>0.2131</v>
       </c>
       <c r="AG31">
-        <v>0.7065</v>
+        <v>0.9465</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>0.4</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3709,65 +3805,32 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
+      <c r="C32">
+        <v>6.5</v>
+      </c>
+      <c r="D32">
+        <v>102</v>
+      </c>
+      <c r="E32">
+        <v>-120</v>
+      </c>
       <c r="F32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32">
-        <v>823671</v>
+        <v>76</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
+        <v>44</v>
+      </c>
+      <c r="L32">
         <v>6</v>
       </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2968</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>130</v>
-      </c>
-      <c r="P32">
-        <v>4.13</v>
-      </c>
-      <c r="Q32">
-        <v>0.3077</v>
-      </c>
-      <c r="R32">
-        <v>0.394</v>
-      </c>
       <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32">
-        <v>0.2046</v>
-      </c>
-      <c r="U32">
-        <v>0.1916</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2226</v>
-      </c>
-      <c r="X32">
-        <v>0.2234</v>
-      </c>
-      <c r="Y32">
-        <v>0.9625</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3775,23 +3838,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>6.56</v>
-      </c>
       <c r="AE32" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF32">
-        <v>0.3011</v>
-      </c>
-      <c r="AG32">
-        <v>0.916</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>6.56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3801,65 +3849,32 @@
       <c r="B33" t="s">
         <v>95</v>
       </c>
+      <c r="C33">
+        <v>4.5</v>
+      </c>
+      <c r="D33">
+        <v>-102</v>
+      </c>
+      <c r="E33">
+        <v>-103</v>
+      </c>
       <c r="F33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G33">
-        <v>824966</v>
+        <v>92</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33">
-        <v>5.4</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0.2106</v>
-      </c>
-      <c r="N33">
-        <v>5</v>
-      </c>
-      <c r="O33">
-        <v>115</v>
-      </c>
-      <c r="P33">
-        <v>4.19</v>
-      </c>
-      <c r="Q33">
-        <v>0.2174</v>
-      </c>
-      <c r="R33">
-        <v>0.365</v>
+        <v>6</v>
       </c>
       <c r="S33" t="s">
-        <v>69</v>
-      </c>
-      <c r="T33">
-        <v>0.2141</v>
-      </c>
-      <c r="U33">
-        <v>0.2308</v>
-      </c>
-      <c r="V33">
-        <v>9</v>
-      </c>
-      <c r="W33">
-        <v>0.2207</v>
-      </c>
-      <c r="X33">
-        <v>0.2234</v>
-      </c>
-      <c r="Y33">
-        <v>1.0405</v>
+        <v>44</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
       </c>
       <c r="AA33" t="s">
         <v>44</v>
@@ -3867,23 +3882,8 @@
       <c r="AC33" t="s">
         <v>44</v>
       </c>
-      <c r="AD33">
-        <v>4.84</v>
-      </c>
       <c r="AE33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF33">
-        <v>0.2131</v>
-      </c>
-      <c r="AG33">
-        <v>0.9583</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>4.84</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-15.xlsx
+++ b/data/k-props/2026-08-15.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="95">
   <si>
     <t>date</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>Reid Detmers</t>
@@ -875,7 +872,7 @@
         <v>0.2272</v>
       </c>
       <c r="X2">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y2">
         <v>0.9736</v>
@@ -887,7 +884,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -896,13 +893,13 @@
         <v>0.1825</v>
       </c>
       <c r="AG2">
-        <v>0.8097</v>
+        <v>0.8183</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -976,7 +973,7 @@
         <v>0.2366</v>
       </c>
       <c r="X3">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y3">
         <v>1.0768</v>
@@ -988,7 +985,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -997,13 +994,13 @@
         <v>0.2125</v>
       </c>
       <c r="AG3">
-        <v>1.0578</v>
+        <v>1.069</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1077,7 +1074,7 @@
         <v>0.2172</v>
       </c>
       <c r="X4">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y4">
         <v>0.9668</v>
@@ -1089,7 +1086,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1098,13 +1095,13 @@
         <v>0.1731</v>
       </c>
       <c r="AG4">
-        <v>1.094</v>
+        <v>1.1056</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1178,7 +1175,7 @@
         <v>0.1812</v>
       </c>
       <c r="X5">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y5">
         <v>0.9265</v>
@@ -1190,7 +1187,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1199,13 +1196,13 @@
         <v>0.1644</v>
       </c>
       <c r="AG5">
-        <v>1.1201</v>
+        <v>1.1319</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1276,10 +1273,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.1893</v>
+        <v>0.1901</v>
       </c>
       <c r="X6">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y6">
         <v>1.0898</v>
@@ -1291,7 +1288,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="AE6" t="s">
         <v>52</v>
@@ -1300,13 +1297,13 @@
         <v>0.3412</v>
       </c>
       <c r="AG6">
-        <v>1.0743</v>
+        <v>1.0856</v>
       </c>
       <c r="AH6">
         <v>-0.77</v>
       </c>
       <c r="AM6">
-        <v>8.48</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1368,10 +1365,10 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2434</v>
+        <v>0.244</v>
       </c>
       <c r="X7">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y7">
         <v>1.0475</v>
@@ -1383,7 +1380,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1392,13 +1389,13 @@
         <v>0.2198</v>
       </c>
       <c r="AG7">
-        <v>1.1249</v>
+        <v>1.1367</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1469,10 +1466,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2021</v>
+        <v>0.2015</v>
       </c>
       <c r="X8">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y8">
         <v>0.9007</v>
@@ -1484,7 +1481,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1493,13 +1490,13 @@
         <v>0.1277</v>
       </c>
       <c r="AG8">
-        <v>1.0743</v>
+        <v>1.0856</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1540,22 +1537,22 @@
         <v>2</v>
       </c>
       <c r="M9">
-        <v>0.1978</v>
+        <v>0.1964</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="P9">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="Q9">
-        <v>0.2119</v>
+        <v>0.2049</v>
       </c>
       <c r="R9">
-        <v>0.371</v>
+        <v>0.379</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1570,10 +1567,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2164</v>
+        <v>0.2177</v>
       </c>
       <c r="X9">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y9">
         <v>0.9947</v>
@@ -1591,10 +1588,10 @@
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.203</v>
+        <v>0.1996</v>
       </c>
       <c r="AG9">
-        <v>0.9924</v>
+        <v>1.0029</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1671,10 +1668,10 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2248</v>
+        <v>0.2247</v>
       </c>
       <c r="X10">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y10">
         <v>0.9929</v>
@@ -1686,7 +1683,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1695,13 +1692,13 @@
         <v>0.2113</v>
       </c>
       <c r="AG10">
-        <v>1.1376</v>
+        <v>1.1496</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1730,7 +1727,7 @@
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1742,22 +1739,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2399</v>
+        <v>0.2349</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="P11">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>0.2672</v>
+        <v>0.25</v>
       </c>
       <c r="R11">
-        <v>0.367</v>
+        <v>0.39</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1772,10 +1769,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2345</v>
+        <v>0.2362</v>
       </c>
       <c r="X11">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y11">
         <v>1.0233</v>
@@ -1787,22 +1784,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.73</v>
+        <v>5.79</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2499</v>
+        <v>0.2408</v>
       </c>
       <c r="AG11">
-        <v>0.9476</v>
+        <v>0.9577</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.73</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1843,22 +1840,22 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2262</v>
+        <v>0.2206</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="P12">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="Q12">
-        <v>0.1887</v>
+        <v>0.1667</v>
       </c>
       <c r="R12">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
@@ -1876,7 +1873,7 @@
         <v>0.1896</v>
       </c>
       <c r="X12">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y12">
         <v>0.88</v>
@@ -1888,22 +1885,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2132</v>
+        <v>0.2017</v>
       </c>
       <c r="AG12">
-        <v>0.8026</v>
+        <v>0.8111</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1932,7 +1929,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1944,22 +1941,22 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2842</v>
+        <v>0.2882</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="P13">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="Q13">
-        <v>0.3398</v>
+        <v>0.2963</v>
       </c>
       <c r="R13">
-        <v>0.34</v>
+        <v>0.351</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1977,7 +1974,7 @@
         <v>0.2573</v>
       </c>
       <c r="X13">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y13">
         <v>1.0233</v>
@@ -1989,22 +1986,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="AE13" t="s">
         <v>64</v>
       </c>
       <c r="AF13">
-        <v>0.3031</v>
+        <v>0.2911</v>
       </c>
       <c r="AG13">
-        <v>1.1692</v>
+        <v>1.1816</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2045,22 +2042,22 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1991</v>
+        <v>0.2068</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="P14">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="Q14">
-        <v>0.1915</v>
+        <v>0.2222</v>
       </c>
       <c r="R14">
-        <v>0.32</v>
+        <v>0.331</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
@@ -2078,7 +2075,7 @@
         <v>0.2532</v>
       </c>
       <c r="X14">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y14">
         <v>1.076</v>
@@ -2090,22 +2087,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.43</v>
+        <v>4.91</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1966</v>
+        <v>0.2119</v>
       </c>
       <c r="AG14">
-        <v>1.1964</v>
+        <v>1.209</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.43</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2146,22 +2143,22 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1887</v>
+        <v>0.1867</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P15">
         <v>4.43</v>
       </c>
       <c r="Q15">
-        <v>0.1875</v>
+        <v>0.1705</v>
       </c>
       <c r="R15">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
@@ -2179,7 +2176,7 @@
         <v>0.2115</v>
       </c>
       <c r="X15">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y15">
         <v>0.9392</v>
@@ -2191,22 +2188,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.86</v>
+        <v>4.74</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1882</v>
+        <v>0.1804</v>
       </c>
       <c r="AG15">
-        <v>1.193</v>
+        <v>1.2056</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.86</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2238,22 +2235,22 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.1484</v>
+        <v>0.1494</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P16">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="Q16">
-        <v>0.2143</v>
+        <v>0.2105</v>
       </c>
       <c r="R16">
-        <v>0.065</v>
+        <v>0.087</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
@@ -2271,7 +2268,7 @@
         <v>0.2251</v>
       </c>
       <c r="X16">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y16">
         <v>0.88</v>
@@ -2283,22 +2280,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1527</v>
+        <v>0.1547</v>
       </c>
       <c r="AG16">
-        <v>0.6977</v>
+        <v>0.7051</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2339,22 +2336,22 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>0.2529</v>
+        <v>0.256</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="P17">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="Q17">
-        <v>0.2935</v>
+        <v>0.3095</v>
       </c>
       <c r="R17">
-        <v>0.315</v>
+        <v>0.296</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
@@ -2372,7 +2369,7 @@
         <v>0.2154</v>
       </c>
       <c r="X17">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y17">
         <v>1.0658</v>
@@ -2384,22 +2381,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2657</v>
+        <v>0.2719</v>
       </c>
       <c r="AG17">
-        <v>0.7694</v>
+        <v>0.7776</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2428,7 +2425,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2440,22 +2437,22 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2265</v>
+        <v>0.2288</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="P18">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="Q18">
-        <v>0.1792</v>
+        <v>0.188</v>
       </c>
       <c r="R18">
-        <v>0.346</v>
+        <v>0.369</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
@@ -2473,7 +2470,7 @@
         <v>0.2154</v>
       </c>
       <c r="X18">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y18">
         <v>0.9861</v>
@@ -2485,22 +2482,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.3</v>
+        <v>4.38</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2102</v>
+        <v>0.2138</v>
       </c>
       <c r="AG18">
-        <v>0.932</v>
+        <v>0.9419</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.3</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2529,7 +2526,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2541,22 +2538,22 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.16</v>
+        <v>0.1895</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="P19">
-        <v>4.02</v>
+        <v>4.19</v>
       </c>
       <c r="Q19">
-        <v>0.16</v>
+        <v>0.1895</v>
       </c>
       <c r="R19">
-        <v>0.273</v>
+        <v>0.322</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
@@ -2574,7 +2571,7 @@
         <v>0.2251</v>
       </c>
       <c r="X19">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y19">
         <v>0.9867</v>
@@ -2586,22 +2583,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.55</v>
+        <v>4.03</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.16</v>
+        <v>0.1895</v>
       </c>
       <c r="AG19">
-        <v>0.8986</v>
+        <v>0.9081</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>3.55</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2621,7 +2618,7 @@
         <v>42</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2633,22 +2630,22 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.2968</v>
+        <v>0.299</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="P20">
         <v>4.13</v>
       </c>
       <c r="Q20">
-        <v>0.3077</v>
+        <v>0.3095</v>
       </c>
       <c r="R20">
-        <v>0.394</v>
+        <v>0.387</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
@@ -2666,7 +2663,7 @@
         <v>0.2226</v>
       </c>
       <c r="X20">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y20">
         <v>0.9625</v>
@@ -2678,22 +2675,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.48</v>
+        <v>6.53</v>
       </c>
       <c r="AE20" t="s">
         <v>64</v>
       </c>
       <c r="AF20">
-        <v>0.3011</v>
+        <v>0.3031</v>
       </c>
       <c r="AG20">
-        <v>0.9047</v>
+        <v>0.9142</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.48</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2734,7 +2731,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2472</v>
+        <v>0.2461</v>
       </c>
       <c r="N21">
         <v>5</v>
@@ -2743,10 +2740,10 @@
         <v>109</v>
       </c>
       <c r="P21">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="Q21">
-        <v>0.3028</v>
+        <v>0.2661</v>
       </c>
       <c r="R21">
         <v>0.353</v>
@@ -2767,7 +2764,7 @@
         <v>0.2364</v>
       </c>
       <c r="X21">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y21">
         <v>0.9562</v>
@@ -2779,22 +2776,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2668</v>
+        <v>0.2531</v>
       </c>
       <c r="AG21">
-        <v>0.9189</v>
+        <v>0.9286</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2823,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2835,22 +2832,22 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2157</v>
+        <v>0.2195</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="P22">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="Q22">
-        <v>0.1953</v>
+        <v>0.2155</v>
       </c>
       <c r="R22">
-        <v>0.39</v>
+        <v>0.367</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
@@ -2868,7 +2865,7 @@
         <v>0.2352</v>
       </c>
       <c r="X22">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y22">
         <v>1.0844</v>
@@ -2880,22 +2877,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.43</v>
+        <v>5.66</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2077</v>
+        <v>0.218</v>
       </c>
       <c r="AG22">
-        <v>1.0405</v>
+        <v>1.0515</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.43</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2924,7 +2921,7 @@
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2936,22 +2933,22 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.261</v>
+        <v>0.2677</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P23">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
-        <v>0.2476</v>
+        <v>0.233</v>
       </c>
       <c r="R23">
-        <v>0.344</v>
+        <v>0.34</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
@@ -2969,7 +2966,7 @@
         <v>0.2167</v>
       </c>
       <c r="X23">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y23">
         <v>0.9661</v>
@@ -2981,22 +2978,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2564</v>
+        <v>0.2559</v>
       </c>
       <c r="AG23">
-        <v>0.8365</v>
+        <v>0.8454</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3025,7 +3022,7 @@
         <v>42</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3037,22 +3034,22 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.1712</v>
+        <v>0.1716</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="P24">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="Q24">
-        <v>0.1719</v>
+        <v>0.1667</v>
       </c>
       <c r="R24">
-        <v>0.39</v>
+        <v>0.387</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
@@ -3070,7 +3067,7 @@
         <v>0.2086</v>
       </c>
       <c r="X24">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y24">
         <v>0.9928</v>
@@ -3082,22 +3079,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.1715</v>
+        <v>0.1697</v>
       </c>
       <c r="AG24">
-        <v>1.133</v>
+        <v>1.1449</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3126,7 +3123,7 @@
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3138,22 +3135,22 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.193</v>
+        <v>0.1913</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="P25">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="Q25">
-        <v>0.1622</v>
+        <v>0.1776</v>
       </c>
       <c r="R25">
-        <v>0.357</v>
+        <v>0.349</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
@@ -3171,7 +3168,7 @@
         <v>0.1991</v>
       </c>
       <c r="X25">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y25">
         <v>0.88</v>
@@ -3183,22 +3180,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.182</v>
+        <v>0.1865</v>
       </c>
       <c r="AG25">
-        <v>0.7909</v>
+        <v>0.7993</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3239,22 +3236,22 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.4056</v>
+        <v>0.3973</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="P26">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="Q26">
-        <v>0.4528</v>
+        <v>0.4124</v>
       </c>
       <c r="R26">
-        <v>0.346</v>
+        <v>0.327</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
@@ -3272,7 +3269,7 @@
         <v>0.2072</v>
       </c>
       <c r="X26">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y26">
         <v>0.9577</v>
@@ -3284,22 +3281,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>8.84</v>
+        <v>8.44</v>
       </c>
       <c r="AE26" t="s">
         <v>52</v>
       </c>
       <c r="AF26">
-        <v>0.4219</v>
+        <v>0.4022</v>
       </c>
       <c r="AG26">
-        <v>0.9567</v>
+        <v>0.9668</v>
       </c>
       <c r="AH26">
         <v>-0.77</v>
       </c>
       <c r="AM26">
-        <v>8.07</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3340,22 +3337,22 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1911</v>
+        <v>0.1934</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P27">
         <v>4.09</v>
       </c>
       <c r="Q27">
-        <v>0.2479</v>
+        <v>0.2301</v>
       </c>
       <c r="R27">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
@@ -3373,7 +3370,7 @@
         <v>0.2192</v>
       </c>
       <c r="X27">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y27">
         <v>0.9537</v>
@@ -3385,22 +3382,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>5.93</v>
+        <v>5.77</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.2125</v>
+        <v>0.2066</v>
       </c>
       <c r="AG27">
-        <v>1.1697</v>
+        <v>1.182</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>5.93</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3459,13 +3456,13 @@
         <v>0.359</v>
       </c>
       <c r="S28" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2683</v>
+        <v>0.2143</v>
       </c>
       <c r="U28">
-        <v>0.2598</v>
+        <v>0.2251</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -3474,10 +3471,10 @@
         <v>0.2507</v>
       </c>
       <c r="X28">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y28">
-        <v>1.0431</v>
+        <v>1.0238</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3486,7 +3483,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3495,13 +3492,13 @@
         <v>0.1277</v>
       </c>
       <c r="AG28">
-        <v>1.1862</v>
+        <v>0.9577</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3509,7 +3506,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29">
         <v>6.5</v>
@@ -3560,25 +3557,25 @@
         <v>0.338</v>
       </c>
       <c r="S29" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.201</v>
+        <v>0.1902</v>
       </c>
       <c r="U29">
-        <v>0.2039</v>
+        <v>0.1823</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>0.2145</v>
       </c>
       <c r="X29">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y29">
-        <v>0.9609</v>
+        <v>0.9579</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3587,7 +3584,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.83</v>
+        <v>5.56</v>
       </c>
       <c r="AE29" t="s">
         <v>45</v>
@@ -3596,13 +3593,13 @@
         <v>0.2958</v>
       </c>
       <c r="AG29">
-        <v>0.8887</v>
+        <v>0.8497</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>5.83</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3610,7 +3607,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C30">
         <v>6.5</v>
@@ -3622,7 +3619,7 @@
         <v>-138</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>824966</v>
@@ -3661,13 +3658,13 @@
         <v>0.379</v>
       </c>
       <c r="S30" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2569</v>
+        <v>0.2248</v>
       </c>
       <c r="U30">
-        <v>0.2251</v>
+        <v>0.2054</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3676,10 +3673,10 @@
         <v>0.2494</v>
       </c>
       <c r="X30">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y30">
-        <v>1.0317</v>
+        <v>1.057</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3688,22 +3685,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>7.16</v>
+        <v>6.49</v>
       </c>
       <c r="AE30" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AF30">
         <v>0.268</v>
       </c>
       <c r="AG30">
-        <v>1.1359</v>
+        <v>1.0047</v>
       </c>
       <c r="AH30">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>6.39</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3711,10 +3708,10 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G31">
         <v>824966</v>
@@ -3753,13 +3750,13 @@
         <v>0.365</v>
       </c>
       <c r="S31" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="T31">
-        <v>0.2141</v>
+        <v>0.24</v>
       </c>
       <c r="U31">
-        <v>0.2308</v>
+        <v>0.238</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3768,10 +3765,10 @@
         <v>0.2207</v>
       </c>
       <c r="X31">
-        <v>0.2262</v>
+        <v>0.2238</v>
       </c>
       <c r="Y31">
-        <v>1.0405</v>
+        <v>1.1186</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3780,7 +3777,7 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>4.78</v>
+        <v>5.83</v>
       </c>
       <c r="AE31" t="s">
         <v>45</v>
@@ -3789,13 +3786,13 @@
         <v>0.2131</v>
       </c>
       <c r="AG31">
-        <v>0.9465</v>
+        <v>1.0723</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>4.78</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3803,7 +3800,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>6.5</v>
@@ -3847,7 +3844,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -3859,7 +3856,7 @@
         <v>-103</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-15.xlsx
+++ b/data/k-props/2026-08-15.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="99">
   <si>
     <t>date</t>
   </si>
@@ -145,21 +145,30 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
     <t>Michael McGreevy</t>
   </si>
   <si>
     <t>St. Louis Cardinals @ Chicago Cubs</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>Matthew Boyd</t>
   </si>
   <si>
@@ -227,6 +236,9 @@
   </si>
   <si>
     <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Emerson Hancock</t>
@@ -877,17 +889,23 @@
       <c r="Y2">
         <v>0.9736</v>
       </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>-1.28</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>3.22</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.1825</v>
@@ -897,6 +915,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.78</v>
+      </c>
+      <c r="AJ2">
+        <v>0.78</v>
+      </c>
+      <c r="AK2">
+        <v>0.78</v>
+      </c>
+      <c r="AL2">
+        <v>0.78</v>
       </c>
       <c r="AM2">
         <v>3.22</v>
@@ -907,7 +937,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>5.5</v>
@@ -978,17 +1008,23 @@
       <c r="Y3">
         <v>1.0768</v>
       </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>0.25</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD3">
         <v>5.75</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.2125</v>
@@ -998,6 +1034,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-1.75</v>
+      </c>
+      <c r="AJ3">
+        <v>1.75</v>
+      </c>
+      <c r="AK3">
+        <v>-1.75</v>
+      </c>
+      <c r="AL3">
+        <v>1.75</v>
       </c>
       <c r="AM3">
         <v>5.75</v>
@@ -1008,7 +1056,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -1020,7 +1068,7 @@
         <v>-125</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>824644</v>
@@ -1079,17 +1127,23 @@
       <c r="Y4">
         <v>0.9668</v>
       </c>
+      <c r="Z4">
+        <v>6</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB4">
+        <v>0.65</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD4">
         <v>4.15</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.1731</v>
@@ -1099,6 +1153,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>1.85</v>
+      </c>
+      <c r="AJ4">
+        <v>1.85</v>
+      </c>
+      <c r="AK4">
+        <v>1.85</v>
+      </c>
+      <c r="AL4">
+        <v>1.85</v>
       </c>
       <c r="AM4">
         <v>4.15</v>
@@ -1109,7 +1175,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1121,7 +1187,7 @@
         <v>-106</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>824644</v>
@@ -1180,17 +1246,23 @@
       <c r="Y5">
         <v>0.9265</v>
       </c>
+      <c r="Z5">
+        <v>2</v>
+      </c>
       <c r="AA5" t="s">
         <v>44</v>
       </c>
+      <c r="AB5">
+        <v>-0.43</v>
+      </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD5">
         <v>4.07</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.1644</v>
@@ -1200,6 +1272,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>-2.07</v>
+      </c>
+      <c r="AJ5">
+        <v>2.07</v>
+      </c>
+      <c r="AK5">
+        <v>-2.07</v>
+      </c>
+      <c r="AL5">
+        <v>2.07</v>
       </c>
       <c r="AM5">
         <v>4.07</v>
@@ -1210,7 +1294,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>6.5</v>
@@ -1222,7 +1306,7 @@
         <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>822775</v>
@@ -1281,17 +1365,23 @@
       <c r="Y6">
         <v>1.0898</v>
       </c>
+      <c r="Z6">
+        <v>7</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB6">
+        <v>2.08</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>9.35</v>
       </c>
       <c r="AE6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF6">
         <v>0.3412</v>
@@ -1301,6 +1391,18 @@
       </c>
       <c r="AH6">
         <v>-0.77</v>
+      </c>
+      <c r="AI6">
+        <v>-2.35</v>
+      </c>
+      <c r="AJ6">
+        <v>2.35</v>
+      </c>
+      <c r="AK6">
+        <v>-1.58</v>
+      </c>
+      <c r="AL6">
+        <v>1.58</v>
       </c>
       <c r="AM6">
         <v>8.58</v>
@@ -1311,16 +1413,16 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>822775</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I7">
         <v>1.1</v>
@@ -1374,16 +1476,16 @@
         <v>1.0475</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD7">
         <v>1.2</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.2198</v>
@@ -1403,7 +1505,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1415,7 +1517,7 @@
         <v>-140</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>823184</v>
@@ -1474,17 +1576,23 @@
       <c r="Y8">
         <v>0.9007</v>
       </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
       <c r="AA8" t="s">
         <v>44</v>
       </c>
+      <c r="AB8">
+        <v>-0.75</v>
+      </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>2.75</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.1277</v>
@@ -1494,6 +1602,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-1.75</v>
+      </c>
+      <c r="AJ8">
+        <v>1.75</v>
+      </c>
+      <c r="AK8">
+        <v>-1.75</v>
+      </c>
+      <c r="AL8">
+        <v>1.75</v>
       </c>
       <c r="AM8">
         <v>2.75</v>
@@ -1504,7 +1624,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1516,7 +1636,7 @@
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>823184</v>
@@ -1575,17 +1695,23 @@
       <c r="Y9">
         <v>0.9947</v>
       </c>
+      <c r="Z9">
+        <v>7</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB9">
+        <v>-0.43</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD9">
         <v>5.07</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.1996</v>
@@ -1595,6 +1721,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>1.93</v>
+      </c>
+      <c r="AJ9">
+        <v>1.93</v>
+      </c>
+      <c r="AK9">
+        <v>1.93</v>
+      </c>
+      <c r="AL9">
+        <v>1.93</v>
       </c>
       <c r="AM9">
         <v>5.07</v>
@@ -1605,7 +1743,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1617,13 +1755,13 @@
         <v>-164</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>823588</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I10">
         <v>1.9</v>
@@ -1676,17 +1814,23 @@
       <c r="Y10">
         <v>0.9929</v>
       </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>-1.53</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD10">
         <v>1.97</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.2113</v>
@@ -1696,6 +1840,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>-0.97</v>
+      </c>
+      <c r="AJ10">
+        <v>0.97</v>
+      </c>
+      <c r="AK10">
+        <v>-0.97</v>
+      </c>
+      <c r="AL10">
+        <v>0.97</v>
       </c>
       <c r="AM10">
         <v>1.97</v>
@@ -1706,7 +1862,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1718,7 +1874,7 @@
         <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>823588</v>
@@ -1777,17 +1933,23 @@
       <c r="Y11">
         <v>1.0233</v>
       </c>
+      <c r="Z11">
+        <v>7</v>
+      </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB11">
+        <v>0.29</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD11">
         <v>5.79</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.2408</v>
@@ -1797,6 +1959,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>1.21</v>
+      </c>
+      <c r="AJ11">
+        <v>1.21</v>
+      </c>
+      <c r="AK11">
+        <v>1.21</v>
+      </c>
+      <c r="AL11">
+        <v>1.21</v>
       </c>
       <c r="AM11">
         <v>5.79</v>
@@ -1807,7 +1981,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1819,7 +1993,7 @@
         <v>-115</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>822941</v>
@@ -1878,17 +2052,23 @@
       <c r="Y12">
         <v>0.88</v>
       </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>-1.13</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD12">
         <v>3.37</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.2017</v>
@@ -1898,6 +2078,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>-0.37</v>
+      </c>
+      <c r="AJ12">
+        <v>0.37</v>
+      </c>
+      <c r="AK12">
+        <v>-0.37</v>
+      </c>
+      <c r="AL12">
+        <v>0.37</v>
       </c>
       <c r="AM12">
         <v>3.37</v>
@@ -1908,7 +2100,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>6.5</v>
@@ -1920,7 +2112,7 @@
         <v>118</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>822941</v>
@@ -1979,17 +2171,23 @@
       <c r="Y13">
         <v>1.0233</v>
       </c>
+      <c r="Z13">
+        <v>9</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB13">
+        <v>0.3</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD13">
         <v>6.8</v>
       </c>
       <c r="AE13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AF13">
         <v>0.2911</v>
@@ -1999,6 +2197,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>2.2</v>
+      </c>
+      <c r="AJ13">
+        <v>2.2</v>
+      </c>
+      <c r="AK13">
+        <v>2.2</v>
+      </c>
+      <c r="AL13">
+        <v>2.2</v>
       </c>
       <c r="AM13">
         <v>6.8</v>
@@ -2009,7 +2219,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2021,13 +2231,13 @@
         <v>-115</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>824480</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -2080,17 +2290,23 @@
       <c r="Y14">
         <v>1.076</v>
       </c>
+      <c r="Z14">
+        <v>6</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB14">
+        <v>0.41</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD14">
         <v>4.91</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.2119</v>
@@ -2100,6 +2316,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>1.09</v>
+      </c>
+      <c r="AJ14">
+        <v>1.09</v>
+      </c>
+      <c r="AK14">
+        <v>1.09</v>
+      </c>
+      <c r="AL14">
+        <v>1.09</v>
       </c>
       <c r="AM14">
         <v>4.91</v>
@@ -2110,7 +2338,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2122,7 +2350,7 @@
         <v>-135</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>824480</v>
@@ -2181,17 +2409,23 @@
       <c r="Y15">
         <v>0.9392</v>
       </c>
+      <c r="Z15">
+        <v>4</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>-0.76</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD15">
         <v>4.74</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.1804</v>
@@ -2201,6 +2435,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>-0.74</v>
+      </c>
+      <c r="AJ15">
+        <v>0.74</v>
+      </c>
+      <c r="AK15">
+        <v>-0.74</v>
+      </c>
+      <c r="AL15">
+        <v>0.74</v>
       </c>
       <c r="AM15">
         <v>4.74</v>
@@ -2211,16 +2457,16 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G16">
         <v>824400</v>
       </c>
       <c r="H16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -2274,16 +2520,16 @@
         <v>0.88</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD16">
         <v>0.4</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1547</v>
@@ -2303,7 +2549,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>5.5</v>
@@ -2315,7 +2561,7 @@
         <v>-138</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>824400</v>
@@ -2374,17 +2620,23 @@
       <c r="Y17">
         <v>1.0658</v>
       </c>
+      <c r="Z17">
+        <v>7</v>
+      </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB17">
+        <v>-0.83</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AD17">
         <v>4.67</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.2719</v>
@@ -2394,6 +2646,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>2.33</v>
+      </c>
+      <c r="AJ17">
+        <v>2.33</v>
+      </c>
+      <c r="AK17">
+        <v>2.33</v>
+      </c>
+      <c r="AL17">
+        <v>2.33</v>
       </c>
       <c r="AM17">
         <v>4.67</v>
@@ -2404,7 +2668,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2416,7 +2680,7 @@
         <v>-104</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>824157</v>
@@ -2475,17 +2739,23 @@
       <c r="Y18">
         <v>0.9861</v>
       </c>
+      <c r="Z18">
+        <v>8</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB18">
+        <v>-0.12</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD18">
         <v>4.38</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.2138</v>
@@ -2495,6 +2765,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>3.62</v>
+      </c>
+      <c r="AJ18">
+        <v>3.62</v>
+      </c>
+      <c r="AK18">
+        <v>3.62</v>
+      </c>
+      <c r="AL18">
+        <v>3.62</v>
       </c>
       <c r="AM18">
         <v>4.38</v>
@@ -2505,7 +2787,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2517,7 +2799,7 @@
         <v>-135</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>824157</v>
@@ -2576,17 +2858,23 @@
       <c r="Y19">
         <v>0.9867</v>
       </c>
+      <c r="Z19">
+        <v>6</v>
+      </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB19">
+        <v>-0.47</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD19">
         <v>4.03</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.1895</v>
@@ -2596,6 +2884,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>1.97</v>
+      </c>
+      <c r="AJ19">
+        <v>1.97</v>
+      </c>
+      <c r="AK19">
+        <v>1.97</v>
+      </c>
+      <c r="AL19">
+        <v>1.97</v>
       </c>
       <c r="AM19">
         <v>4.03</v>
@@ -2606,10 +2906,10 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>823671</v>
@@ -2669,16 +2969,16 @@
         <v>0.9625</v>
       </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD20">
         <v>6.53</v>
       </c>
       <c r="AE20" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AF20">
         <v>0.3031</v>
@@ -2698,7 +2998,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>5.5</v>
@@ -2710,7 +3010,7 @@
         <v>-140</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>823671</v>
@@ -2769,17 +3069,23 @@
       <c r="Y21">
         <v>0.9562</v>
       </c>
+      <c r="Z21">
+        <v>6</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB21">
+        <v>-0.45</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD21">
         <v>5.05</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.2531</v>
@@ -2789,6 +3095,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0.95</v>
+      </c>
+      <c r="AJ21">
+        <v>0.95</v>
+      </c>
+      <c r="AK21">
+        <v>0.95</v>
+      </c>
+      <c r="AL21">
+        <v>0.95</v>
       </c>
       <c r="AM21">
         <v>5.05</v>
@@ -2799,7 +3117,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2811,7 +3129,7 @@
         <v>-113</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>823347</v>
@@ -2870,17 +3188,23 @@
       <c r="Y22">
         <v>1.0844</v>
       </c>
+      <c r="Z22">
+        <v>7</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB22">
+        <v>0.16</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD22">
         <v>5.66</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.218</v>
@@ -2890,6 +3214,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>1.34</v>
+      </c>
+      <c r="AJ22">
+        <v>1.34</v>
+      </c>
+      <c r="AK22">
+        <v>1.34</v>
+      </c>
+      <c r="AL22">
+        <v>1.34</v>
       </c>
       <c r="AM22">
         <v>5.66</v>
@@ -2900,7 +3236,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>4.5</v>
@@ -2912,7 +3248,7 @@
         <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>823347</v>
@@ -2971,17 +3307,23 @@
       <c r="Y23">
         <v>0.9661</v>
       </c>
+      <c r="Z23">
+        <v>7</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB23">
+        <v>-0.48</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD23">
         <v>4.02</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.2559</v>
@@ -2991,6 +3333,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>2.98</v>
+      </c>
+      <c r="AJ23">
+        <v>2.98</v>
+      </c>
+      <c r="AK23">
+        <v>2.98</v>
+      </c>
+      <c r="AL23">
+        <v>2.98</v>
       </c>
       <c r="AM23">
         <v>4.02</v>
@@ -3001,7 +3355,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -3013,7 +3367,7 @@
         <v>-149</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>824884</v>
@@ -3072,17 +3426,23 @@
       <c r="Y24">
         <v>0.9928</v>
       </c>
+      <c r="Z24">
+        <v>5</v>
+      </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB24">
+        <v>0.18</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD24">
         <v>4.68</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.1697</v>
@@ -3092,6 +3452,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0.32</v>
+      </c>
+      <c r="AJ24">
+        <v>0.32</v>
+      </c>
+      <c r="AK24">
+        <v>0.32</v>
+      </c>
+      <c r="AL24">
+        <v>0.32</v>
       </c>
       <c r="AM24">
         <v>4.68</v>
@@ -3102,7 +3474,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>3.5</v>
@@ -3114,7 +3486,7 @@
         <v>115</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25">
         <v>824884</v>
@@ -3173,17 +3545,23 @@
       <c r="Y25">
         <v>0.88</v>
       </c>
+      <c r="Z25">
+        <v>3</v>
+      </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>-0.71</v>
+      </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD25">
         <v>2.79</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.1865</v>
@@ -3193,6 +3571,18 @@
       </c>
       <c r="AH25">
         <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0.21</v>
+      </c>
+      <c r="AJ25">
+        <v>0.21</v>
+      </c>
+      <c r="AK25">
+        <v>0.21</v>
+      </c>
+      <c r="AL25">
+        <v>0.21</v>
       </c>
       <c r="AM25">
         <v>2.79</v>
@@ -3203,7 +3593,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>8.5</v>
@@ -3215,7 +3605,7 @@
         <v>-104</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G26">
         <v>823914</v>
@@ -3274,17 +3664,23 @@
       <c r="Y26">
         <v>0.9577</v>
       </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
       <c r="AA26" t="s">
         <v>44</v>
       </c>
+      <c r="AB26">
+        <v>-0.83</v>
+      </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD26">
         <v>8.44</v>
       </c>
       <c r="AE26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF26">
         <v>0.4022</v>
@@ -3294,6 +3690,18 @@
       </c>
       <c r="AH26">
         <v>-0.77</v>
+      </c>
+      <c r="AI26">
+        <v>-2.44</v>
+      </c>
+      <c r="AJ26">
+        <v>2.44</v>
+      </c>
+      <c r="AK26">
+        <v>-1.67</v>
+      </c>
+      <c r="AL26">
+        <v>1.67</v>
       </c>
       <c r="AM26">
         <v>7.67</v>
@@ -3304,7 +3712,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3316,7 +3724,7 @@
         <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G27">
         <v>823914</v>
@@ -3375,17 +3783,23 @@
       <c r="Y27">
         <v>0.9537</v>
       </c>
+      <c r="Z27">
+        <v>6</v>
+      </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB27">
+        <v>1.27</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD27">
         <v>5.77</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>0.2066</v>
@@ -3395,6 +3809,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0.23</v>
+      </c>
+      <c r="AJ27">
+        <v>0.23</v>
+      </c>
+      <c r="AK27">
+        <v>0.23</v>
+      </c>
+      <c r="AL27">
+        <v>0.23</v>
       </c>
       <c r="AM27">
         <v>5.77</v>
@@ -3405,7 +3831,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>3.5</v>
@@ -3417,7 +3843,7 @@
         <v>-150</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G28">
         <v>823990</v>
@@ -3476,17 +3902,23 @@
       <c r="Y28">
         <v>1.0238</v>
       </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB28">
+        <v>-0.7</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AD28">
         <v>2.8</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF28">
         <v>0.1277</v>
@@ -3496,6 +3928,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>3.2</v>
+      </c>
+      <c r="AJ28">
+        <v>3.2</v>
+      </c>
+      <c r="AK28">
+        <v>3.2</v>
+      </c>
+      <c r="AL28">
+        <v>3.2</v>
       </c>
       <c r="AM28">
         <v>2.8</v>
@@ -3506,7 +3950,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>6.5</v>
@@ -3518,7 +3962,7 @@
         <v>-132</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G29">
         <v>823990</v>
@@ -3577,17 +4021,23 @@
       <c r="Y29">
         <v>0.9579</v>
       </c>
+      <c r="Z29">
+        <v>11</v>
+      </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB29">
+        <v>-0.94</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AD29">
         <v>5.56</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF29">
         <v>0.2958</v>
@@ -3597,6 +4047,18 @@
       </c>
       <c r="AH29">
         <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>5.44</v>
+      </c>
+      <c r="AJ29">
+        <v>5.44</v>
+      </c>
+      <c r="AK29">
+        <v>5.44</v>
+      </c>
+      <c r="AL29">
+        <v>5.44</v>
       </c>
       <c r="AM29">
         <v>5.56</v>
@@ -3607,7 +4069,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>6.5</v>
@@ -3619,7 +4081,7 @@
         <v>-138</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G30">
         <v>824966</v>
@@ -3678,17 +4140,23 @@
       <c r="Y30">
         <v>1.057</v>
       </c>
+      <c r="Z30">
+        <v>5</v>
+      </c>
       <c r="AA30" t="s">
         <v>44</v>
       </c>
+      <c r="AB30">
+        <v>-0.01</v>
+      </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD30">
         <v>6.49</v>
       </c>
       <c r="AE30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AF30">
         <v>0.268</v>
@@ -3698,6 +4166,18 @@
       </c>
       <c r="AH30">
         <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>-1.49</v>
+      </c>
+      <c r="AJ30">
+        <v>1.49</v>
+      </c>
+      <c r="AK30">
+        <v>-1.49</v>
+      </c>
+      <c r="AL30">
+        <v>1.49</v>
       </c>
       <c r="AM30">
         <v>6.49</v>
@@ -3708,10 +4188,10 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G31">
         <v>824966</v>
@@ -3771,16 +4251,16 @@
         <v>1.1186</v>
       </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD31">
         <v>5.83</v>
       </c>
       <c r="AE31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF31">
         <v>0.2131</v>
@@ -3800,7 +4280,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>6.5</v>
@@ -3812,31 +4292,31 @@
         <v>-120</v>
       </c>
       <c r="F32" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3844,7 +4324,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -3856,31 +4336,31 @@
         <v>-103</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L33">
         <v>6</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
